--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2026.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>142618.76</v>
+        <v>143973.48</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4113.14</v>
+        <v>4152.21</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>64438.36</v>
+        <v>65050.46</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2466.49</v>
+        <v>2489.91</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3967.98</v>
+        <v>4005.67</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6076.71</v>
+        <v>6134.43</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15220.8</v>
+        <v>15365.38</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3511.72</v>
+        <v>3545.08</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3580.47</v>
+        <v>3614.48</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3007.48</v>
+        <v>3036.05</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>813.47</v>
+        <v>821.2</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1078.51</v>
+        <v>1088.76</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1771.82</v>
+        <v>1788.65</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>858.6</v>
+        <v>866.76</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1599.43</v>
+        <v>1614.62</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1281.09</v>
+        <v>1293.26</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5088.5</v>
+        <v>5136.84</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1703.94</v>
+        <v>1720.13</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6249.94</v>
+        <v>6309.31</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2372.05</v>
+        <v>2394.58</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>7571.44</v>
+        <v>7643.36</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>28073</v>
+        <v>28339.67</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>12265.96</v>
+        <v>12382.47</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2181.56</v>
+        <v>2202.28</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>781.79</v>
+        <v>789.22</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6499.15</v>
+        <v>6560.89</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1344.75</v>
+        <v>1357.52</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1714.48</v>
+        <v>1730.77</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>780.95</v>
+        <v>788.37</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11032.72</v>
+        <v>11137.52</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3829.92</v>
+        <v>3866.3</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1945.28</v>
+        <v>1963.76</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5131.23</v>
+        <v>5179.97</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3641.22</v>
+        <v>3675.81</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2595.82</v>
+        <v>2620.47</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>899.24</v>
+        <v>907.78</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2186.18</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2244.69</v>
+        <v>2266.01</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>778.47</v>
+        <v>781.51</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2649.15</v>
+        <v>2659.49</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3327.6</v>
+        <v>3340.58</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1403.27</v>
+        <v>1408.75</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2649.93</v>
+        <v>2660.27</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2098.51</v>
+        <v>2106.7</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>33799.13</v>
+        <v>33931.07</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>859.59</v>
+        <v>862.9400000000001</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6076.1</v>
+        <v>6099.82</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4982.69</v>
+        <v>5002.14</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3273.82</v>
+        <v>3286.6</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>15742.07</v>
+        <v>15803.52</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1079.34</v>
+        <v>1083.56</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1883.45</v>
+        <v>1890.8</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3062.45</v>
+        <v>3074.4</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>15413.37</v>
+        <v>15473.54</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5901.94</v>
+        <v>5924.98</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2372.21</v>
+        <v>2381.47</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2667.04</v>
+        <v>2677.45</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1011.44</v>
+        <v>1015.38</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2197.55</v>
+        <v>2206.12</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1456.7</v>
+        <v>1462.38</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>10409.54</v>
+        <v>10450.17</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>39193.93</v>
+        <v>39346.93</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2642.48</v>
+        <v>2652.79</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1151.95</v>
+        <v>1156.45</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>771.97</v>
+        <v>774.98</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1228.18</v>
+        <v>1232.98</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>16263.12</v>
+        <v>16326.6</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>974.4</v>
+        <v>978.2</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2416.9</v>
+        <v>2426.33</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1062.53</v>
+        <v>1066.68</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1111.11</v>
+        <v>1115.45</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>19237.46</v>
+        <v>19312.56</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>860.64</v>
+        <v>864</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6708.83</v>
+        <v>6735.01</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>15634.28</v>
+        <v>15695.31</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7061.04</v>
+        <v>7088.6</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1221.42</v>
+        <v>1226.18</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1073.53</v>
+        <v>1084.33</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>802.62</v>
+        <v>810.7</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9647.389999999999</v>
+        <v>9744.42</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1478.28</v>
+        <v>1493.15</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12075.28</v>
+        <v>12196.73</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3092.99</v>
+        <v>3124.1</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>774.15</v>
+        <v>781.9400000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1897.31</v>
+        <v>1916.39</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>10229.09</v>
+        <v>10331.97</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2618.8</v>
+        <v>2645.14</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7140.22</v>
+        <v>7212.04</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3333.77</v>
+        <v>3367.3</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2737.93</v>
+        <v>2765.47</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2551.05</v>
+        <v>2576.71</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>794.78</v>
+        <v>802.77</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2643.65</v>
+        <v>2670.24</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2089.2</v>
+        <v>2110.21</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1141.6</v>
+        <v>1153.08</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1286.4</v>
+        <v>1299.33</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3312.77</v>
+        <v>3346.09</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2378.91</v>
+        <v>2402.84</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>770.36</v>
+        <v>778.11</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>787.22</v>
+        <v>795.14</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1388.98</v>
+        <v>1402.95</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2188.09</v>
+        <v>2210.1</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2659.81</v>
+        <v>2686.56</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1374.94</v>
+        <v>1388.76</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2176.25</v>
+        <v>2198.14</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1409.31</v>
+        <v>1423.48</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1819.38</v>
+        <v>1837.68</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>8458.860000000001</v>
+        <v>8543.93</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>989.85</v>
+        <v>999.8099999999999</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8203.34</v>
+        <v>8285.84</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>5547.68</v>
+        <v>5603.47</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1128.82</v>
+        <v>1140.17</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1436.54</v>
+        <v>1450.99</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>781.39</v>
+        <v>789.25</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>76269.91</v>
+        <v>77036.99000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6375.06</v>
+        <v>6439.18</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1176.55</v>
+        <v>1188.39</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2644.8</v>
+        <v>2671.4</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>9842.42</v>
+        <v>9941.41</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>786.15</v>
+        <v>794.0599999999999</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>5351.23</v>
+        <v>5405.05</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4780.99</v>
+        <v>4829.07</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>26353.41</v>
+        <v>26618.46</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2787.83</v>
+        <v>2815.87</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>926.12</v>
+        <v>935.4400000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1860.35</v>
+        <v>1879.06</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>10170.49</v>
+        <v>10272.78</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>841.92</v>
+        <v>850.39</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6390.77</v>
+        <v>6455.05</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2786.28</v>
+        <v>2814.3</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3061.06</v>
+        <v>3091.84</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>777.1</v>
+        <v>784.92</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1998.73</v>
+        <v>2018.83</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3464.43</v>
+        <v>3499.27</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2220.99</v>
+        <v>2243.33</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>771.13</v>
+        <v>778.85</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>5003.02</v>
+        <v>5053.12</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3046.69</v>
+        <v>3077.2</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4023.89</v>
+        <v>4064.18</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2855.02</v>
+        <v>2883.61</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1072.5</v>
+        <v>1083.24</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2427.91</v>
+        <v>2452.22</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3418.83</v>
+        <v>3453.06</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1418.58</v>
+        <v>1432.79</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1923.86</v>
+        <v>1943.13</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1619.25</v>
+        <v>1635.47</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>6768.82</v>
+        <v>6836.6</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3504.11</v>
+        <v>3539.2</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>14807.48</v>
+        <v>14955.75</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>6606.95</v>
+        <v>6673.11</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1746.84</v>
+        <v>1764.33</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2046.71</v>
+        <v>2067.21</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1634.15</v>
+        <v>1650.51</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2321.35</v>
+        <v>2344.59</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>4069.25</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1937.82</v>
+        <v>1957.23</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2360.98</v>
+        <v>2384.62</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>936.3099999999999</v>
+        <v>945.6900000000001</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2008.44</v>
+        <v>2028.55</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3761.85</v>
+        <v>3799.52</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4806.68</v>
+        <v>4854.81</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2876.88</v>
+        <v>2905.69</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1089.04</v>
+        <v>1099.94</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>18453.89</v>
+        <v>18638.68</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6819.39</v>
+        <v>6887.68</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5383.46</v>
+        <v>5437.37</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4916.66</v>
+        <v>4965.89</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7891.07</v>
+        <v>7970.09</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2193.02</v>
+        <v>2214.98</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>31254.17</v>
+        <v>31567.13</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3602.31</v>
+        <v>3638.39</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1959.59</v>
+        <v>1979.21</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>993.1</v>
+        <v>1003.04</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>14549.71</v>
+        <v>14695.4</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>786.83</v>
+        <v>794.71</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3046.33</v>
+        <v>3076.83</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>35308.25</v>
+        <v>35661.81</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5211.42</v>
+        <v>5263.61</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2352.27</v>
+        <v>2375.82</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1513.94</v>
+        <v>1529.1</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>50140.05</v>
+        <v>50642.14</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>769.8</v>
+        <v>777.5</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1436.31</v>
+        <v>1450.69</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2647.13</v>
+        <v>2673.63</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1161.22</v>
+        <v>1172.85</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2931.9</v>
+        <v>2961.26</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8306.35</v>
+        <v>8348.68</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1796.69</v>
+        <v>1805.85</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3484.34</v>
+        <v>3502.09</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>13144.21</v>
+        <v>13211.19</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>970.73</v>
+        <v>975.6799999999999</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2319.62</v>
+        <v>2331.44</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3629.78</v>
+        <v>3648.28</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2353.55</v>
+        <v>2365.55</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2309.37</v>
+        <v>2321.14</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2453.49</v>
+        <v>2465.99</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1557.43</v>
+        <v>1565.37</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1549.22</v>
+        <v>1557.12</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>786.88</v>
+        <v>790.89</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2252.11</v>
+        <v>2263.59</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>897.5</v>
+        <v>902.0700000000001</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>7494.52</v>
+        <v>7532.71</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2027.78</v>
+        <v>2038.12</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1065.22</v>
+        <v>1070.64</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1603.23</v>
+        <v>1611.4</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1020.06</v>
+        <v>1025.25</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1426.51</v>
+        <v>1433.78</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>6235.34</v>
+        <v>6267.11</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2463.13</v>
+        <v>2475.68</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2487.86</v>
+        <v>2500.54</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1794.58</v>
+        <v>1803.72</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>21482.81</v>
+        <v>21592.29</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1993.36</v>
+        <v>2003.52</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3012.91</v>
+        <v>3028.27</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>4624.61</v>
+        <v>4648.17</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5163.31</v>
+        <v>5189.62</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>779.21</v>
+        <v>783.1799999999999</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3504.38</v>
+        <v>3522.24</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>5327.86</v>
+        <v>5355.01</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>18475.85</v>
+        <v>18570</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>8575.540000000001</v>
+        <v>8619.24</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>960.3</v>
+        <v>965.1900000000001</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>11301.66</v>
+        <v>11359.25</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>9548.24</v>
+        <v>9596.889999999999</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>807.42</v>
+        <v>811.53</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2942.29</v>
+        <v>2957.28</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>9128.790000000001</v>
+        <v>9175.309999999999</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>21525.9</v>
+        <v>21635.59</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>13236.64</v>
+        <v>13304.09</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2121.26</v>
+        <v>2132.07</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>10463.2</v>
+        <v>10516.52</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>5565</v>
+        <v>5586.66</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1263.38</v>
+        <v>1268.3</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>936.67</v>
+        <v>940.3099999999999</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4691.81</v>
+        <v>4710.07</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>893.26</v>
+        <v>896.74</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2343.57</v>
+        <v>2352.69</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4680.2</v>
+        <v>4698.42</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2171.22</v>
+        <v>2179.68</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>7463.45</v>
+        <v>7492.5</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>3025.79</v>
+        <v>3037.57</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1054.49</v>
+        <v>1058.59</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1663.09</v>
+        <v>1669.56</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>22509.75</v>
+        <v>22597.37</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>797.62</v>
+        <v>800.72</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4188.11</v>
+        <v>4204.41</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1045.89</v>
+        <v>1049.96</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3006.44</v>
+        <v>3018.15</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>6596.31</v>
+        <v>6621.99</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4196.71</v>
+        <v>4213.04</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1061.45</v>
+        <v>1065.58</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>855.62</v>
+        <v>858.95</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1280.22</v>
+        <v>1285.2</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1591.9</v>
+        <v>1598.1</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>7519.74</v>
+        <v>7549.01</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3928.02</v>
+        <v>3943.31</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6202.37</v>
+        <v>6226.51</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>3093.23</v>
+        <v>3105.27</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1004.58</v>
+        <v>1008.49</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2015.33</v>
+        <v>2023.18</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>9863.23</v>
+        <v>9901.629999999999</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>766.05</v>
+        <v>769.03</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>3640.42</v>
+        <v>3654.59</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2424.43</v>
+        <v>2433.87</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1043.22</v>
+        <v>1047.28</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1064.82</v>
+        <v>1068.97</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4118.58</v>
+        <v>4134.61</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>2079.79</v>
+        <v>2087.89</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4112.67</v>
+        <v>4128.68</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3577</v>
+        <v>3590.93</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1443.31</v>
+        <v>1448.93</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1530.59</v>
+        <v>1536.54</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1299.07</v>
+        <v>1304.13</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1488.34</v>
+        <v>1494.13</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5389.67</v>
+        <v>5410.65</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2086.36</v>
+        <v>2094.49</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1055.21</v>
+        <v>1059.32</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1066.43</v>
+        <v>1070.58</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5650.88</v>
+        <v>5672.88</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>854.58</v>
+        <v>857.9</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>41463.65</v>
+        <v>41625.06</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3001.83</v>
+        <v>3013.51</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>12853.31</v>
+        <v>12903.34</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>5837.31</v>
+        <v>5860.03</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1030.34</v>
+        <v>1034.35</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1074.63</v>
+        <v>1078.81</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1571.38</v>
+        <v>1577.5</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>4915.2</v>
+        <v>4934.33</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1526.79</v>
+        <v>1532.74</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>16086.43</v>
+        <v>16004.94</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>853.6900000000001</v>
+        <v>849.37</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>4039.23</v>
+        <v>4018.77</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3099.72</v>
+        <v>3084.02</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>4294.88</v>
+        <v>4273.12</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2256.09</v>
+        <v>2244.66</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2920.09</v>
+        <v>2905.3</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>839.72</v>
+        <v>835.46</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3255.13</v>
+        <v>3238.64</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>807.55</v>
+        <v>803.46</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1927.64</v>
+        <v>1917.88</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2752.48</v>
+        <v>2738.54</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2220.3</v>
+        <v>2209.05</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>12326.25</v>
+        <v>12263.81</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3245.98</v>
+        <v>3229.53</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1524.11</v>
+        <v>1516.38</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1822.25</v>
+        <v>1813.02</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1074.08</v>
+        <v>1068.64</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>10798.54</v>
+        <v>10743.84</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1537.67</v>
+        <v>1529.88</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1203.31</v>
+        <v>1197.21</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>5681.82</v>
+        <v>5653.03</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1342.11</v>
+        <v>1335.31</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>21820.95</v>
+        <v>21710.42</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>1077.27</v>
+        <v>1071.82</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>13836.51</v>
+        <v>13766.42</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1827.47</v>
+        <v>1818.21</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2691.7</v>
+        <v>2678.06</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1665.49</v>
+        <v>1657.05</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>782.63</v>
+        <v>778.66</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3651.26</v>
+        <v>3632.76</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>3150.98</v>
+        <v>3135.02</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>1991.13</v>
+        <v>1981.05</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>770.9400000000001</v>
+        <v>767.04</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1423.87</v>
+        <v>1416.65</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>14859.62</v>
+        <v>14784.34</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1342.03</v>
+        <v>1335.24</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1464.13</v>
+        <v>1456.71</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1029.2</v>
+        <v>1023.98</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>5748.43</v>
+        <v>5719.31</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>889.27</v>
+        <v>884.76</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1960.84</v>
+        <v>1950.91</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>1584.93</v>
+        <v>1576.9</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>1496.84</v>
+        <v>1489.26</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>3652.65</v>
+        <v>3634.15</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2521.13</v>
+        <v>2508.36</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>25357.78</v>
+        <v>25229.33</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4516.98</v>
+        <v>4494.1</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>8893.459999999999</v>
+        <v>8912.41</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2311.49</v>
+        <v>2316.41</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>1019.47</v>
+        <v>1021.64</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>31852.97</v>
+        <v>31920.85</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2305.04</v>
+        <v>2309.96</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>6412.66</v>
+        <v>6426.33</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>15182.59</v>
+        <v>15214.95</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>17192.07</v>
+        <v>17228.72</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>963.83</v>
+        <v>965.88</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>1989.53</v>
+        <v>1993.77</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>6735.8</v>
+        <v>6750.15</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>21774.91</v>
+        <v>21821.32</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3684.85</v>
+        <v>3692.7</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2553.82</v>
+        <v>2559.26</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1282.17</v>
+        <v>1284.91</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1713.6</v>
+        <v>1717.26</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>7051.06</v>
+        <v>7066.08</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>4334.12</v>
+        <v>4343.36</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>26351.67</v>
+        <v>26407.83</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>18268.44</v>
+        <v>18307.38</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>3022.44</v>
+        <v>3028.88</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3587.75</v>
+        <v>3595.4</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1730.74</v>
+        <v>1734.43</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>3062.92</v>
+        <v>3069.45</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2956.07</v>
+        <v>2962.37</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>4756.29</v>
+        <v>4766.42</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>937.54</v>
+        <v>939.53</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>55107.83</v>
+        <v>55225.28</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>6012.83</v>
+        <v>6025.64</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2834.3</v>
+        <v>2840.34</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>929.98</v>
+        <v>931.97</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>1687.09</v>
+        <v>1690.69</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>829.61</v>
+        <v>831.38</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>12050.58</v>
+        <v>12076.26</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4509.56</v>
+        <v>4519.17</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1158.94</v>
+        <v>1161.41</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>955.3099999999999</v>
+        <v>957.34</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>15291.67</v>
+        <v>15324.27</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>1608.92</v>
+        <v>1612.35</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>956.85</v>
+        <v>958.89</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>74899.56</v>
+        <v>75059.19</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>29558.29</v>
+        <v>29621.29</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>12034.08</v>
+        <v>12059.72</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>8183.27</v>
+        <v>8200.709999999999</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>25211</v>
+        <v>25264.73</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1341.33</v>
+        <v>1344.19</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>773.85</v>
+        <v>775.5</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>16593.56</v>
+        <v>16628.92</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1719.73</v>
+        <v>1723.4</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>996.0700000000001</v>
+        <v>998.1900000000001</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>980.66</v>
+        <v>982.75</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>11424.74</v>
+        <v>11449.09</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>7167.24</v>
+        <v>7182.51</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>4381.69</v>
+        <v>4391.03</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>7136.4</v>
+        <v>7151.61</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1857.02</v>
+        <v>1860.98</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>6031.58</v>
+        <v>6044.44</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1388.17</v>
+        <v>1391.12</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3387.84</v>
+        <v>3409.92</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>1154.75</v>
+        <v>1162.28</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1235.75</v>
+        <v>1243.8</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1261.01</v>
+        <v>1269.23</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>6364.27</v>
+        <v>6405.76</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>4210.51</v>
+        <v>4237.96</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2406.82</v>
+        <v>2422.51</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>4147.98</v>
+        <v>4175.02</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>1041.76</v>
+        <v>1048.55</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1676.38</v>
+        <v>1687.31</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>769.73</v>
+        <v>774.75</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1004.26</v>
+        <v>1010.81</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>7134.6</v>
+        <v>7181.11</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>25739.02</v>
+        <v>25906.82</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1396.61</v>
+        <v>1405.71</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>4763.09</v>
+        <v>4794.15</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2481.38</v>
+        <v>2497.56</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>779.34</v>
+        <v>784.42</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>33349.51</v>
+        <v>33566.93</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1631.78</v>
+        <v>1642.42</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>3435.18</v>
+        <v>3457.58</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2269.74</v>
+        <v>2284.54</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1799.44</v>
+        <v>1811.17</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>1305.34</v>
+        <v>1313.85</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>2211.3</v>
+        <v>2225.71</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>5621.61</v>
+        <v>5658.26</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>4027.35</v>
+        <v>4053.61</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>9626.790000000001</v>
+        <v>9689.549999999999</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>5572.6</v>
+        <v>5608.93</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>819.1</v>
+        <v>824.4400000000001</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>10691.93</v>
+        <v>10761.64</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>1006.24</v>
+        <v>1012.8</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>4989.75</v>
+        <v>5022.28</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>7253.99</v>
+        <v>7301.28</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>5261.5</v>
+        <v>5295.8</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1640.94</v>
+        <v>1651.63</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>1047.9</v>
+        <v>1054.73</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>1008.17</v>
+        <v>1014.74</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>1004.69</v>
+        <v>1011.24</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>784.28</v>
+        <v>789.39</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>4029.47</v>
+        <v>4055.74</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>1280.79</v>
+        <v>1289.14</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>774.53</v>
+        <v>779.58</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>14762.65</v>
+        <v>14858.89</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3071.65</v>
+        <v>3091.67</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1392.33</v>
+        <v>1401.41</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>1959.73</v>
+        <v>1972.5</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>4890.42</v>
+        <v>4922.31</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>5836.58</v>
+        <v>5874.63</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>3754.17</v>
+        <v>3762.78</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>937.33</v>
+        <v>939.48</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>941.83</v>
+        <v>943.99</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3715.25</v>
+        <v>3723.77</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>7300.65</v>
+        <v>7317.39</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>3496.38</v>
+        <v>3504.4</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>4105.54</v>
+        <v>4114.95</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>10736.29</v>
+        <v>10760.91</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1984.07</v>
+        <v>1988.62</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>6133.89</v>
+        <v>6147.96</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1074.09</v>
+        <v>1076.55</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>4929.9</v>
+        <v>4941.21</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1439.07</v>
+        <v>1442.37</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>4963.51</v>
+        <v>4974.89</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>1257.78</v>
+        <v>1260.67</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>19208.49</v>
+        <v>19252.54</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>5585.89</v>
+        <v>5598.7</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>8893.459999999999</v>
+        <v>8913.85</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>852.34</v>
+        <v>854.3</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>1239.05</v>
+        <v>1241.89</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>4899.23</v>
+        <v>4910.46</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>1229.91</v>
+        <v>1232.73</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>6148.86</v>
+        <v>6162.96</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>825.1900000000001</v>
+        <v>827.08</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>3733.07</v>
+        <v>3741.63</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>4471.46</v>
+        <v>4481.71</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>6141.34</v>
+        <v>6155.43</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>1527.49</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>6643.33</v>
+        <v>6658.57</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>4232.11</v>
+        <v>4241.82</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>3577.66</v>
+        <v>3585.86</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>1269.05</v>
+        <v>1271.96</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>5424.58</v>
+        <v>5437.02</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>2037.19</v>
+        <v>2041.86</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>2166.27</v>
+        <v>2171.24</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>6398.29</v>
+        <v>6412.96</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>2849.32</v>
+        <v>2855.86</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>1054.42</v>
+        <v>1056.84</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>11014.82</v>
+        <v>11040.08</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>4392.02</v>
+        <v>4402.09</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>2017.13</v>
+        <v>2021.76</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>3209.13</v>
+        <v>3216.49</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>848.8099999999999</v>
+        <v>850.75</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>2949.2</v>
+        <v>2955.96</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>20732.49</v>
+        <v>20780.03</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>1311.92</v>
+        <v>1314.93</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>4422.7</v>
+        <v>4432.84</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1816.84</v>
+        <v>1821.01</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>6175.61</v>
+        <v>6189.77</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>10269.92</v>
+        <v>10293.47</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>780.03</v>
+        <v>781.8099999999999</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>16360.96</v>
+        <v>16398.48</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>1937.62</v>
+        <v>1942.06</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>770.46</v>
+        <v>772.22</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1373.03</v>
+        <v>1376.18</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1026.9</v>
+        <v>1029.26</v>
       </c>
     </row>
     <row r="502">
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>132491.08</v>
+        <v>132794.91</v>
       </c>
     </row>
     <row r="503">
@@ -31138,7 +31138,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1908.3</v>
+        <v>1912.68</v>
       </c>
     </row>
     <row r="504">
@@ -31199,7 +31199,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>3642.92</v>
+        <v>3667.31</v>
       </c>
     </row>
     <row r="505">
@@ -31260,7 +31260,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>15310.21</v>
+        <v>15412.69</v>
       </c>
     </row>
     <row r="506">
@@ -31321,7 +31321,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>4663.97</v>
+        <v>4695.18</v>
       </c>
     </row>
     <row r="507">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>1263.59</v>
+        <v>1272.05</v>
       </c>
     </row>
     <row r="508">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>7628.4</v>
+        <v>7679.46</v>
       </c>
     </row>
     <row r="509">
@@ -31504,7 +31504,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>2312.42</v>
+        <v>2327.9</v>
       </c>
     </row>
     <row r="510">
@@ -31565,7 +31565,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>7302.18</v>
+        <v>7351.06</v>
       </c>
     </row>
     <row r="511">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1232.1</v>
+        <v>1240.35</v>
       </c>
     </row>
     <row r="512">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>3491.57</v>
+        <v>3514.94</v>
       </c>
     </row>
     <row r="513">
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>6567.67</v>
+        <v>6611.63</v>
       </c>
     </row>
     <row r="514">
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3375.32</v>
+        <v>3397.91</v>
       </c>
     </row>
     <row r="515">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>6509.89</v>
+        <v>6553.47</v>
       </c>
     </row>
     <row r="516">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>8948.23</v>
+        <v>9008.129999999999</v>
       </c>
     </row>
     <row r="517">
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>1887.64</v>
+        <v>1900.28</v>
       </c>
     </row>
     <row r="518">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>977.85</v>
+        <v>984.4</v>
       </c>
     </row>
     <row r="519">
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1942.38</v>
+        <v>1955.38</v>
       </c>
     </row>
     <row r="520">
@@ -32175,7 +32175,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>39590.88</v>
+        <v>39855.88</v>
       </c>
     </row>
     <row r="521">
@@ -32236,7 +32236,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2255.59</v>
+        <v>2270.68</v>
       </c>
     </row>
     <row r="522">
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>5073.14</v>
+        <v>5107.1</v>
       </c>
     </row>
     <row r="523">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>15277.48</v>
+        <v>15379.74</v>
       </c>
     </row>
     <row r="524">
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>2425.65</v>
+        <v>2441.88</v>
       </c>
     </row>
     <row r="525">
@@ -32480,7 +32480,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>57486.14</v>
+        <v>57870.92</v>
       </c>
     </row>
     <row r="526">
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1226.42</v>
+        <v>1234.63</v>
       </c>
     </row>
     <row r="527">
@@ -32602,7 +32602,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>1274.19</v>
+        <v>1282.71</v>
       </c>
     </row>
     <row r="528">
@@ -32663,7 +32663,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>2226.93</v>
+        <v>2241.84</v>
       </c>
     </row>
     <row r="529">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1597.12</v>
+        <v>1607.81</v>
       </c>
     </row>
     <row r="530">
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2716.89</v>
+        <v>2735.08</v>
       </c>
     </row>
     <row r="531">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1088.61</v>
+        <v>1095.9</v>
       </c>
     </row>
     <row r="532">
@@ -32907,7 +32907,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2995.14</v>
+        <v>3015.19</v>
       </c>
     </row>
     <row r="533">
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2154.21</v>
+        <v>2168.63</v>
       </c>
     </row>
     <row r="534">
@@ -33029,7 +33029,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2088.17</v>
+        <v>2102.15</v>
       </c>
     </row>
     <row r="535">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1978.56</v>
+        <v>1991.8</v>
       </c>
     </row>
     <row r="536">
@@ -33151,7 +33151,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>2550.91</v>
+        <v>2567.99</v>
       </c>
     </row>
     <row r="537">
@@ -33212,7 +33212,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>909.83</v>
+        <v>915.92</v>
       </c>
     </row>
     <row r="538">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>3269.08</v>
+        <v>3290.96</v>
       </c>
     </row>
     <row r="539">
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1431.05</v>
+        <v>1440.63</v>
       </c>
     </row>
     <row r="540">
@@ -33395,7 +33395,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>773.16</v>
+        <v>778.34</v>
       </c>
     </row>
     <row r="541">
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>15971.57</v>
+        <v>16078.47</v>
       </c>
     </row>
     <row r="542">
@@ -33517,7 +33517,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>9820.67</v>
+        <v>9886.4</v>
       </c>
     </row>
     <row r="543">
@@ -33578,7 +33578,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>21528.05</v>
+        <v>21672.14</v>
       </c>
     </row>
     <row r="544">
@@ -33639,7 +33639,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>4886.56</v>
+        <v>4919.27</v>
       </c>
     </row>
     <row r="545">
@@ -33700,7 +33700,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>888.4299999999999</v>
+        <v>894.38</v>
       </c>
     </row>
     <row r="546">
@@ -33761,7 +33761,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>5406.14</v>
+        <v>5442.32</v>
       </c>
     </row>
     <row r="547">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2340.71</v>
+        <v>2356.37</v>
       </c>
     </row>
     <row r="548">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>13382.77</v>
+        <v>13472.35</v>
       </c>
     </row>
     <row r="549">
@@ -33944,7 +33944,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>10006.68</v>
+        <v>10073.66</v>
       </c>
     </row>
     <row r="550">
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>3480.05</v>
+        <v>3503.34</v>
       </c>
     </row>
     <row r="551">
@@ -34066,7 +34066,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>3969.35</v>
+        <v>3995.92</v>
       </c>
     </row>
     <row r="552">
@@ -34127,7 +34127,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1279.39</v>
+        <v>1287.95</v>
       </c>
     </row>
     <row r="553">
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>2148.36</v>
+        <v>2162.74</v>
       </c>
     </row>
     <row r="554">
@@ -34249,7 +34249,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>11463.21</v>
+        <v>11539.94</v>
       </c>
     </row>
     <row r="555">
@@ -34310,7 +34310,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>4541.36</v>
+        <v>4571.76</v>
       </c>
     </row>
     <row r="556">
@@ -34371,7 +34371,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>945.1</v>
+        <v>951.4299999999999</v>
       </c>
     </row>
     <row r="557">
@@ -34432,7 +34432,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1720.31</v>
+        <v>1731.82</v>
       </c>
     </row>
     <row r="558">
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2036.82</v>
+        <v>2050.46</v>
       </c>
     </row>
     <row r="559">
@@ -34554,7 +34554,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2087.31</v>
+        <v>2101.28</v>
       </c>
     </row>
     <row r="560">
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>3353.58</v>
+        <v>3376.03</v>
       </c>
     </row>
     <row r="561">
@@ -34676,7 +34676,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1112.65</v>
+        <v>1120.1</v>
       </c>
     </row>
     <row r="562">
@@ -34737,7 +34737,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>4026.13</v>
+        <v>4053.07</v>
       </c>
     </row>
     <row r="563">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>61563.41</v>
+        <v>61975.49</v>
       </c>
     </row>
     <row r="564">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>23192.55</v>
+        <v>23347.79</v>
       </c>
     </row>
     <row r="565">
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1400.19</v>
+        <v>1409.56</v>
       </c>
     </row>
     <row r="566">
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>3255.64</v>
+        <v>3277.43</v>
       </c>
     </row>
     <row r="567">
@@ -35042,7 +35042,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>981.28</v>
+        <v>987.85</v>
       </c>
     </row>
     <row r="568">
@@ -35103,7 +35103,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>12480.19</v>
+        <v>12563.73</v>
       </c>
     </row>
     <row r="569">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>871.1799999999999</v>
+        <v>877.01</v>
       </c>
     </row>
     <row r="570">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>63635.57</v>
+        <v>64061.52</v>
       </c>
     </row>
     <row r="571">
@@ -35286,7 +35286,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>2739.59</v>
+        <v>2757.93</v>
       </c>
     </row>
     <row r="572">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>836.22</v>
+        <v>841.8200000000001</v>
       </c>
     </row>
     <row r="573">
@@ -35408,7 +35408,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1324.5</v>
+        <v>1333.77</v>
       </c>
     </row>
     <row r="574">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>3013.21</v>
+        <v>3034.3</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1785.73</v>
+        <v>1798.22</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>1988.04</v>
+        <v>2001.95</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>2157.66</v>
+        <v>2172.76</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>37467.86</v>
+        <v>37730.07</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1259.47</v>
+        <v>1268.29</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>1548.2</v>
+        <v>1559.04</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>4884.49</v>
+        <v>4918.67</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>1300.03</v>
+        <v>1309.13</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>7359.7</v>
+        <v>7411.21</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>5898.26</v>
+        <v>5939.54</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>9845.719999999999</v>
+        <v>9914.620000000001</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>3624.05</v>
+        <v>3649.41</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1678.21</v>
+        <v>1689.95</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>1899.72</v>
+        <v>1913.01</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>34079.07</v>
+        <v>34317.57</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>3661.8</v>
+        <v>3687.42</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>3161.33</v>
+        <v>3183.46</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>898.3099999999999</v>
+        <v>904.6</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>13592.77</v>
+        <v>13687.9</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>11383.31</v>
+        <v>11462.98</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1156.75</v>
+        <v>1164.85</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1999.69</v>
+        <v>2013.69</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>1839</v>
+        <v>1851.87</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1078.45</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1055.82</v>
+        <v>1063.21</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1157.43</v>
+        <v>1165.53</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>8437.51</v>
+        <v>8410.860000000001</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>1934.46</v>
+        <v>1928.35</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2557.78</v>
+        <v>2549.7</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>1775.9</v>
+        <v>1770.29</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>1765.99</v>
+        <v>1760.41</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>779.34</v>
+        <v>776.88</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1137.82</v>
+        <v>1134.23</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>4280</v>
+        <v>4266.48</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>1265.74</v>
+        <v>1261.74</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>2259.35</v>
+        <v>2252.21</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2438.58</v>
+        <v>2430.88</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>831.4</v>
+        <v>828.78</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>855.04</v>
+        <v>852.34</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>1325.28</v>
+        <v>1321.09</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>4548.99</v>
+        <v>4534.62</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>770.27</v>
+        <v>767.84</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>1682.59</v>
+        <v>1677.28</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>1296.74</v>
+        <v>1292.64</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>2714.91</v>
+        <v>2706.34</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>1628.07</v>
+        <v>1622.93</v>
       </c>
     </row>
     <row r="621">
@@ -38340,7 +38340,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>108773.97</v>
+        <v>108430.38</v>
       </c>
     </row>
     <row r="622">
@@ -38401,7 +38401,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>811.65</v>
+        <v>809.08</v>
       </c>
     </row>
     <row r="623">
@@ -38462,7 +38462,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>859.45</v>
+        <v>856.73</v>
       </c>
     </row>
     <row r="624">
@@ -38523,7 +38523,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1595.07</v>
+        <v>1590.03</v>
       </c>
     </row>
     <row r="625">
@@ -38584,7 +38584,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>7579.61</v>
+        <v>7555.67</v>
       </c>
     </row>
     <row r="626">
@@ -38645,7 +38645,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>22440.72</v>
+        <v>22369.84</v>
       </c>
     </row>
     <row r="627">
@@ -38706,7 +38706,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>1667.54</v>
+        <v>1662.28</v>
       </c>
     </row>
     <row r="628">
@@ -38767,7 +38767,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>6349.39</v>
+        <v>6329.33</v>
       </c>
     </row>
     <row r="629">
@@ -38828,7 +38828,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>8451.27</v>
+        <v>8424.57</v>
       </c>
     </row>
     <row r="630">
@@ -38889,7 +38889,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>3706.25</v>
+        <v>3694.54</v>
       </c>
     </row>
     <row r="631">
@@ -38950,7 +38950,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>1179.96</v>
+        <v>1176.23</v>
       </c>
     </row>
     <row r="632">
@@ -39011,7 +39011,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>3659.4</v>
+        <v>3647.85</v>
       </c>
     </row>
     <row r="633">
@@ -39072,7 +39072,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>780.09</v>
+        <v>777.62</v>
       </c>
     </row>
     <row r="634">
@@ -39133,7 +39133,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>2418.05</v>
+        <v>2410.42</v>
       </c>
     </row>
     <row r="635">
@@ -39194,7 +39194,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>4862.41</v>
+        <v>4847.05</v>
       </c>
     </row>
     <row r="636">
@@ -39255,7 +39255,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2553.73</v>
+        <v>2548.17</v>
       </c>
     </row>
     <row r="637">
@@ -39316,7 +39316,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>819.48</v>
+        <v>817.6900000000001</v>
       </c>
     </row>
     <row r="638">
@@ -39377,7 +39377,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1073.08</v>
+        <v>1070.74</v>
       </c>
     </row>
     <row r="639">
@@ -39438,7 +39438,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>2889.35</v>
+        <v>2883.06</v>
       </c>
     </row>
     <row r="640">
@@ -39499,7 +39499,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>3071.04</v>
+        <v>3064.36</v>
       </c>
     </row>
     <row r="641">
@@ -39560,7 +39560,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>6082.62</v>
+        <v>6069.38</v>
       </c>
     </row>
     <row r="642">
@@ -39621,7 +39621,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>5622.88</v>
+        <v>5610.65</v>
       </c>
     </row>
     <row r="643">
@@ -39682,7 +39682,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>936.39</v>
+        <v>934.35</v>
       </c>
     </row>
     <row r="644">
@@ -39743,7 +39743,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>919.96</v>
+        <v>917.96</v>
       </c>
     </row>
     <row r="645">
@@ -39804,7 +39804,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1672.08</v>
+        <v>1668.44</v>
       </c>
     </row>
     <row r="646">
@@ -39865,7 +39865,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>1092.38</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="647">
@@ -39926,7 +39926,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>1092.38</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="648">
@@ -39987,7 +39987,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>1262.52</v>
+        <v>1259.77</v>
       </c>
     </row>
     <row r="649">
@@ -40048,7 +40048,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>2184.76</v>
+        <v>2180.01</v>
       </c>
     </row>
     <row r="650">
@@ -40109,7 +40109,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>11678.57</v>
+        <v>11653.16</v>
       </c>
     </row>
     <row r="651">
@@ -40170,7 +40170,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>25777.49</v>
+        <v>25721.4</v>
       </c>
     </row>
     <row r="652">
@@ -40231,7 +40231,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>1263.32</v>
+        <v>1260.57</v>
       </c>
     </row>
     <row r="653">
@@ -40292,7 +40292,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>7413.06</v>
+        <v>7396.93</v>
       </c>
     </row>
     <row r="654">
@@ -40353,7 +40353,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>6437.84</v>
+        <v>6423.83</v>
       </c>
     </row>
     <row r="655">
@@ -40414,7 +40414,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>2577.54</v>
+        <v>2571.93</v>
       </c>
     </row>
     <row r="656">
@@ -40475,7 +40475,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>3016</v>
+        <v>3009.44</v>
       </c>
     </row>
     <row r="657">
@@ -40536,7 +40536,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1092.38</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="658">
@@ -40597,7 +40597,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>11077.98</v>
+        <v>11053.88</v>
       </c>
     </row>
     <row r="659">
@@ -40658,7 +40658,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1017.08</v>
+        <v>1014.86</v>
       </c>
     </row>
     <row r="660">
@@ -40719,7 +40719,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2451.38</v>
+        <v>2446.04</v>
       </c>
     </row>
     <row r="661">
@@ -40780,7 +40780,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>829.23</v>
+        <v>827.4299999999999</v>
       </c>
     </row>
     <row r="662">
@@ -40841,7 +40841,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>955.36</v>
+        <v>953.28</v>
       </c>
     </row>
     <row r="663">
@@ -40902,7 +40902,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>1080.05</v>
+        <v>1077.7</v>
       </c>
     </row>
     <row r="664">
@@ -40963,7 +40963,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>788.37</v>
+        <v>786.65</v>
       </c>
     </row>
     <row r="665">
@@ -41024,7 +41024,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>6632.69</v>
+        <v>6618.26</v>
       </c>
     </row>
     <row r="666">
@@ -41085,7 +41085,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>6130.86</v>
+        <v>6117.52</v>
       </c>
     </row>
     <row r="667">
@@ -41146,7 +41146,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>14058.12</v>
+        <v>14027.53</v>
       </c>
     </row>
     <row r="668">
@@ -41207,7 +41207,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>6799.77</v>
+        <v>6784.98</v>
       </c>
     </row>
     <row r="669">
@@ -41268,7 +41268,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>2420.76</v>
+        <v>2415.49</v>
       </c>
     </row>
     <row r="670">
@@ -41329,7 +41329,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>3284.99</v>
+        <v>3277.84</v>
       </c>
     </row>
     <row r="671">
@@ -41390,7 +41390,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>827.63</v>
+        <v>825.83</v>
       </c>
     </row>
     <row r="672">
@@ -41451,7 +41451,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>1453.63</v>
+        <v>1450.47</v>
       </c>
     </row>
     <row r="673">
@@ -41512,7 +41512,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>2175.56</v>
+        <v>2170.83</v>
       </c>
     </row>
     <row r="674">
@@ -41573,7 +41573,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>1169.97</v>
+        <v>1167.42</v>
       </c>
     </row>
     <row r="675">
@@ -41634,7 +41634,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2017.06</v>
+        <v>2012.67</v>
       </c>
     </row>
     <row r="676">
@@ -41695,7 +41695,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>4796.69</v>
+        <v>4786.26</v>
       </c>
     </row>
     <row r="677">
@@ -41756,7 +41756,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>4153.82</v>
+        <v>4144.78</v>
       </c>
     </row>
     <row r="678">
@@ -41817,7 +41817,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>1808.62</v>
+        <v>1804.68</v>
       </c>
     </row>
     <row r="679">
@@ -41878,7 +41878,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>6544.3</v>
+        <v>6530.06</v>
       </c>
     </row>
     <row r="680">
@@ -41939,7 +41939,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>769.95</v>
+        <v>768.27</v>
       </c>
     </row>
     <row r="681">
@@ -42000,7 +42000,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>1707.83</v>
+        <v>1704.11</v>
       </c>
     </row>
     <row r="682">
@@ -42061,7 +42061,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1002.56</v>
+        <v>1000.38</v>
       </c>
     </row>
     <row r="683">
@@ -42122,7 +42122,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>1290.41</v>
+        <v>1287.82</v>
       </c>
     </row>
     <row r="684">
@@ -42183,7 +42183,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>11117.85</v>
+        <v>11095.56</v>
       </c>
     </row>
     <row r="685">
@@ -42244,7 +42244,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>812.1900000000001</v>
+        <v>810.5599999999999</v>
       </c>
     </row>
     <row r="686">
@@ -42305,7 +42305,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>857.3200000000001</v>
+        <v>855.6</v>
       </c>
     </row>
     <row r="687">
@@ -42366,7 +42366,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>978.85</v>
+        <v>976.89</v>
       </c>
     </row>
     <row r="688">
@@ -42427,7 +42427,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>788.42</v>
+        <v>786.84</v>
       </c>
     </row>
     <row r="689">
@@ -42488,7 +42488,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>45873.52</v>
+        <v>45781.56</v>
       </c>
     </row>
     <row r="690">
@@ -42549,7 +42549,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>7913</v>
+        <v>7897.14</v>
       </c>
     </row>
     <row r="691">
@@ -42610,7 +42610,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>14987.18</v>
+        <v>14957.14</v>
       </c>
     </row>
     <row r="692">
@@ -42671,7 +42671,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>912.72</v>
+        <v>910.89</v>
       </c>
     </row>
     <row r="693">
@@ -42732,7 +42732,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>781.85</v>
+        <v>780.28</v>
       </c>
     </row>
     <row r="694">
@@ -42793,7 +42793,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>2680.78</v>
+        <v>2675.41</v>
       </c>
     </row>
     <row r="695">
@@ -42854,7 +42854,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>2944.72</v>
+        <v>2938.82</v>
       </c>
     </row>
     <row r="696">
@@ -42915,7 +42915,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>847.26</v>
+        <v>845.5599999999999</v>
       </c>
     </row>
     <row r="697">
@@ -42976,7 +42976,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>4667.19</v>
+        <v>4657.83</v>
       </c>
     </row>
     <row r="698">
@@ -43037,7 +43037,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>6257.48</v>
+        <v>6244.94</v>
       </c>
     </row>
     <row r="699">
@@ -43098,7 +43098,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>5207.89</v>
+        <v>5197.45</v>
       </c>
     </row>
     <row r="700">
@@ -43159,7 +43159,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>22241.7</v>
+        <v>22197.12</v>
       </c>
     </row>
     <row r="701">
@@ -43220,7 +43220,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>1287.2</v>
+        <v>1284.62</v>
       </c>
     </row>
     <row r="702">
@@ -43281,7 +43281,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>3793.37</v>
+        <v>3785.77</v>
       </c>
     </row>
     <row r="703">
@@ -43342,7 +43342,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>4998.24</v>
+        <v>4988.22</v>
       </c>
     </row>
     <row r="704">
@@ -43403,7 +43403,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>1007.25</v>
+        <v>1005.23</v>
       </c>
     </row>
     <row r="705">
@@ -43464,7 +43464,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>10203.67</v>
+        <v>10183.22</v>
       </c>
     </row>
     <row r="706">
@@ -43525,7 +43525,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>8867.299999999999</v>
+        <v>8849.530000000001</v>
       </c>
     </row>
     <row r="707">
@@ -43586,7 +43586,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>18560</v>
+        <v>18522.79</v>
       </c>
     </row>
     <row r="708">
@@ -43647,7 +43647,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>3812.27</v>
+        <v>3804.63</v>
       </c>
     </row>
     <row r="709">
@@ -43708,7 +43708,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>7672.49</v>
+        <v>7657.11</v>
       </c>
     </row>
     <row r="710">
@@ -43769,7 +43769,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>2895.33</v>
+        <v>2889.53</v>
       </c>
     </row>
     <row r="711">
@@ -43830,7 +43830,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>7667.35</v>
+        <v>7651.98</v>
       </c>
     </row>
     <row r="712">
@@ -43891,7 +43891,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>2095.26</v>
+        <v>2091.06</v>
       </c>
     </row>
     <row r="713">
@@ -43952,7 +43952,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>12462.81</v>
+        <v>12437.82</v>
       </c>
     </row>
     <row r="714">
@@ -44013,7 +44013,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>799.21</v>
+        <v>797.61</v>
       </c>
     </row>
     <row r="715">
@@ -44074,7 +44074,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>75543.69</v>
+        <v>75392.25</v>
       </c>
     </row>
     <row r="716">
@@ -44135,7 +44135,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2422.12</v>
+        <v>2417.26</v>
       </c>
     </row>
     <row r="717">
@@ -44196,7 +44196,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>987.11</v>
+        <v>985.13</v>
       </c>
     </row>
     <row r="718">
@@ -44257,7 +44257,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>8232.799999999999</v>
+        <v>8216.299999999999</v>
       </c>
     </row>
     <row r="719">
@@ -44318,7 +44318,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>3453.21</v>
+        <v>3446.29</v>
       </c>
     </row>
     <row r="720">
@@ -44379,7 +44379,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>10710.03</v>
+        <v>10688.56</v>
       </c>
     </row>
     <row r="721">
@@ -44440,7 +44440,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>956.66</v>
+        <v>954.74</v>
       </c>
     </row>
     <row r="722">
@@ -44501,7 +44501,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>6084.58</v>
+        <v>6072.38</v>
       </c>
     </row>
     <row r="723">
@@ -44562,7 +44562,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>7641.04</v>
+        <v>7625.73</v>
       </c>
     </row>
     <row r="724">
@@ -44623,7 +44623,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>2115.69</v>
+        <v>2111.45</v>
       </c>
     </row>
     <row r="725">
@@ -44684,7 +44684,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>5042.55</v>
+        <v>5032.45</v>
       </c>
     </row>
     <row r="726">
@@ -44745,7 +44745,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>1639.77</v>
+        <v>1636.48</v>
       </c>
     </row>
     <row r="727">
@@ -44806,7 +44806,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>1809.14</v>
+        <v>1805.51</v>
       </c>
     </row>
     <row r="728">
@@ -44867,7 +44867,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>858.1900000000001</v>
+        <v>856.47</v>
       </c>
     </row>
     <row r="729">
@@ -44928,7 +44928,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2620.83</v>
+        <v>2615.58</v>
       </c>
     </row>
     <row r="730">
@@ -44989,7 +44989,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>12158.53</v>
+        <v>12088.16</v>
       </c>
     </row>
     <row r="731">
@@ -45050,7 +45050,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>19059.76</v>
+        <v>18949.44</v>
       </c>
     </row>
     <row r="732">
@@ -45111,7 +45111,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>2661.29</v>
+        <v>2645.88</v>
       </c>
     </row>
     <row r="733">
@@ -45172,7 +45172,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>9664.73</v>
+        <v>9608.790000000001</v>
       </c>
     </row>
     <row r="734">
@@ -45233,7 +45233,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>3757.39</v>
+        <v>3735.64</v>
       </c>
     </row>
     <row r="735">
@@ -45294,7 +45294,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>7511.69</v>
+        <v>7468.21</v>
       </c>
     </row>
     <row r="736">
@@ -45355,7 +45355,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>8898.32</v>
+        <v>8846.809999999999</v>
       </c>
     </row>
     <row r="737">
@@ -45416,7 +45416,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>2439.73</v>
+        <v>2425.61</v>
       </c>
     </row>
     <row r="738">
@@ -45477,7 +45477,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>1051.34</v>
+        <v>1045.25</v>
       </c>
     </row>
     <row r="739">
@@ -45538,7 +45538,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>2223.49</v>
+        <v>2210.62</v>
       </c>
     </row>
     <row r="740">
@@ -45599,7 +45599,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>1985.36</v>
+        <v>1973.87</v>
       </c>
     </row>
     <row r="741">
@@ -45660,7 +45660,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>4012.64</v>
+        <v>3989.42</v>
       </c>
     </row>
     <row r="742">
@@ -45721,7 +45721,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>2203.27</v>
+        <v>2190.52</v>
       </c>
     </row>
     <row r="743">
@@ -45782,7 +45782,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1524.92</v>
+        <v>1516.09</v>
       </c>
     </row>
     <row r="744">
@@ -45843,7 +45843,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>2781.24</v>
+        <v>2765.14</v>
       </c>
     </row>
     <row r="745">
@@ -45904,7 +45904,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>5296.5</v>
+        <v>5265.84</v>
       </c>
     </row>
     <row r="746">
@@ -45965,7 +45965,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>909.13</v>
+        <v>903.87</v>
       </c>
     </row>
     <row r="747">
@@ -46026,7 +46026,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>2395.87</v>
+        <v>2382.01</v>
       </c>
     </row>
     <row r="748">
@@ -46087,7 +46087,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>68818</v>
+        <v>68419.67</v>
       </c>
     </row>
     <row r="749">
@@ -46148,7 +46148,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>2831.57</v>
+        <v>2815.18</v>
       </c>
     </row>
     <row r="750">
@@ -46209,7 +46209,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>1239.37</v>
+        <v>1232.19</v>
       </c>
     </row>
     <row r="751">
@@ -46270,7 +46270,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>1953.66</v>
+        <v>1942.35</v>
       </c>
     </row>
     <row r="752">
@@ -46331,7 +46331,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>3546.85</v>
+        <v>3526.32</v>
       </c>
     </row>
     <row r="753">
@@ -46392,7 +46392,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>14670.97</v>
+        <v>14586.06</v>
       </c>
     </row>
     <row r="754">
@@ -46453,7 +46453,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>15067.34</v>
+        <v>14980.13</v>
       </c>
     </row>
     <row r="755">
@@ -46514,7 +46514,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>1464.89</v>
+        <v>1456.41</v>
       </c>
     </row>
     <row r="756">
@@ -46575,7 +46575,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>810.8099999999999</v>
+        <v>806.12</v>
       </c>
     </row>
     <row r="757">
@@ -46636,7 +46636,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>1832.84</v>
+        <v>1822.24</v>
       </c>
     </row>
     <row r="758">
@@ -46697,7 +46697,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>4659.17</v>
+        <v>4632.2</v>
       </c>
     </row>
     <row r="759">
@@ -46758,7 +46758,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>3115.16</v>
+        <v>3097.13</v>
       </c>
     </row>
     <row r="760">
@@ -46819,7 +46819,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>1071.26</v>
+        <v>1065.06</v>
       </c>
     </row>
     <row r="761">
@@ -46880,7 +46880,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>2140.93</v>
+        <v>2128.54</v>
       </c>
     </row>
     <row r="762">
@@ -46945,7 +46945,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>65477.67</v>
+        <v>65098.68</v>
       </c>
     </row>
     <row r="763">
@@ -47006,7 +47006,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>1525.64</v>
+        <v>1516.81</v>
       </c>
     </row>
     <row r="764">
@@ -47067,7 +47067,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>1772.55</v>
+        <v>1762.29</v>
       </c>
     </row>
     <row r="765">
@@ -47128,7 +47128,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>1223.71</v>
+        <v>1216.63</v>
       </c>
     </row>
     <row r="766">
@@ -47189,7 +47189,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>972.23</v>
+        <v>966.61</v>
       </c>
     </row>
     <row r="767">
@@ -47250,7 +47250,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>1470.71</v>
+        <v>1462.2</v>
       </c>
     </row>
     <row r="768">
@@ -47311,7 +47311,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>1605.18</v>
+        <v>1595.89</v>
       </c>
     </row>
     <row r="769">
@@ -47372,7 +47372,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>1626.83</v>
+        <v>1617.41</v>
       </c>
     </row>
     <row r="770">
@@ -47433,7 +47433,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>1895.88</v>
+        <v>1884.91</v>
       </c>
     </row>
     <row r="771">
@@ -47494,7 +47494,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>57798.21</v>
+        <v>57463.66</v>
       </c>
     </row>
     <row r="772">
@@ -47555,7 +47555,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>2616.74</v>
+        <v>2601.6</v>
       </c>
     </row>
     <row r="773">
@@ -47616,7 +47616,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>5971.28</v>
+        <v>5936.72</v>
       </c>
     </row>
     <row r="774">
@@ -47677,7 +47677,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>984.1799999999999</v>
+        <v>978.48</v>
       </c>
     </row>
     <row r="775">
@@ -47738,7 +47738,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>45505.23</v>
+        <v>45241.83</v>
       </c>
     </row>
     <row r="776">
@@ -47799,7 +47799,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>3097.68</v>
+        <v>3079.75</v>
       </c>
     </row>
     <row r="777">
@@ -47860,7 +47860,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>4528.33</v>
+        <v>4502.12</v>
       </c>
     </row>
     <row r="778">
@@ -47921,7 +47921,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>6057.49</v>
+        <v>6022.43</v>
       </c>
     </row>
     <row r="779">
@@ -47982,7 +47982,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>53532.55</v>
+        <v>53222.7</v>
       </c>
     </row>
     <row r="780">
@@ -48043,7 +48043,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>782.89</v>
+        <v>778.36</v>
       </c>
     </row>
     <row r="781">
@@ -48104,7 +48104,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>5606.21</v>
+        <v>5573.76</v>
       </c>
     </row>
     <row r="782">
@@ -48165,7 +48165,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>3585.24</v>
+        <v>3564.49</v>
       </c>
     </row>
     <row r="783">
@@ -48226,7 +48226,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>773.65</v>
+        <v>769.17</v>
       </c>
     </row>
     <row r="784">
@@ -48287,7 +48287,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>4057.79</v>
+        <v>4034.3</v>
       </c>
     </row>
     <row r="785">
@@ -48348,7 +48348,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>2673.69</v>
+        <v>2658.21</v>
       </c>
     </row>
     <row r="786">
@@ -48409,7 +48409,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>1668.11</v>
+        <v>1658.46</v>
       </c>
     </row>
     <row r="787">
@@ -48470,7 +48470,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>1339.51</v>
+        <v>1331.76</v>
       </c>
     </row>
     <row r="788">
@@ -48531,7 +48531,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>11406.37</v>
+        <v>11340.35</v>
       </c>
     </row>
     <row r="789">
@@ -48592,7 +48592,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>23890.33</v>
+        <v>23752.05</v>
       </c>
     </row>
     <row r="790">
@@ -48653,7 +48653,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>832.4</v>
+        <v>827.59</v>
       </c>
     </row>
     <row r="791">
@@ -48714,7 +48714,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>56021.89</v>
+        <v>55697.63</v>
       </c>
     </row>
     <row r="792">
@@ -48775,7 +48775,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>1883.79</v>
+        <v>1872.89</v>
       </c>
     </row>
     <row r="793">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>2027.25</v>
+        <v>2015.51</v>
       </c>
     </row>
     <row r="794">
@@ -48897,7 +48897,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>823.21</v>
+        <v>818.45</v>
       </c>
     </row>
     <row r="795">
@@ -48958,7 +48958,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>773.09</v>
+        <v>760.62</v>
       </c>
     </row>
     <row r="796">
@@ -49019,7 +49019,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>3134.95</v>
+        <v>3084.36</v>
       </c>
     </row>
     <row r="797">
@@ -49080,7 +49080,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>7051.39</v>
+        <v>6937.6</v>
       </c>
     </row>
     <row r="798">
@@ -49141,7 +49141,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>5461.91</v>
+        <v>5373.76</v>
       </c>
     </row>
     <row r="799">
@@ -49202,7 +49202,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>2449.05</v>
+        <v>2409.52</v>
       </c>
     </row>
     <row r="800">
@@ -49263,7 +49263,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>2966.22</v>
+        <v>2918.36</v>
       </c>
     </row>
     <row r="801">
@@ -49324,7 +49324,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>6309.3</v>
+        <v>6207.49</v>
       </c>
     </row>
     <row r="802">
@@ -49385,7 +49385,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>1866.23</v>
+        <v>1836.11</v>
       </c>
     </row>
     <row r="803">
@@ -49446,7 +49446,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>6828.56</v>
+        <v>6718.36</v>
       </c>
     </row>
     <row r="804">
@@ -49507,7 +49507,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>1401.28</v>
+        <v>1378.67</v>
       </c>
     </row>
     <row r="805">
@@ -49568,7 +49568,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>1820.28</v>
+        <v>1790.91</v>
       </c>
     </row>
     <row r="806">
@@ -49629,7 +49629,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>2754.71</v>
+        <v>2710.25</v>
       </c>
     </row>
     <row r="807">
@@ -49690,7 +49690,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>4338.72</v>
+        <v>4268.7</v>
       </c>
     </row>
     <row r="808">
@@ -49751,7 +49751,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>73800.81</v>
+        <v>72609.85000000001</v>
       </c>
     </row>
     <row r="809">
@@ -49812,7 +49812,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>1881.9</v>
+        <v>1851.53</v>
       </c>
     </row>
     <row r="810">
@@ -49873,7 +49873,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>6841.22</v>
+        <v>6730.82</v>
       </c>
     </row>
     <row r="811">
@@ -49934,7 +49934,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>5347.35</v>
+        <v>5261.06</v>
       </c>
     </row>
     <row r="812">
@@ -49995,7 +49995,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>1430.57</v>
+        <v>1407.48</v>
       </c>
     </row>
     <row r="813">
@@ -50056,7 +50056,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>1261.24</v>
+        <v>1240.88</v>
       </c>
     </row>
     <row r="814">
@@ -50117,7 +50117,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>2874.88</v>
+        <v>2828.49</v>
       </c>
     </row>
     <row r="815">
@@ -50178,7 +50178,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>2952.25</v>
+        <v>2904.61</v>
       </c>
     </row>
     <row r="816">
@@ -50239,7 +50239,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>3356.18</v>
+        <v>3302.02</v>
       </c>
     </row>
     <row r="817">
@@ -50300,7 +50300,7 @@
         </is>
       </c>
       <c r="M817" s="2" t="n">
-        <v>3395.64</v>
+        <v>3340.84</v>
       </c>
     </row>
     <row r="818">
@@ -50361,7 +50361,7 @@
         </is>
       </c>
       <c r="M818" s="2" t="n">
-        <v>3962.47</v>
+        <v>3898.53</v>
       </c>
     </row>
     <row r="819">
@@ -50422,7 +50422,7 @@
         </is>
       </c>
       <c r="M819" s="2" t="n">
-        <v>892.98</v>
+        <v>878.5700000000001</v>
       </c>
     </row>
     <row r="820">
@@ -50483,7 +50483,7 @@
         </is>
       </c>
       <c r="M820" s="2" t="n">
-        <v>2358</v>
+        <v>2319.94</v>
       </c>
     </row>
     <row r="821">
@@ -50544,7 +50544,7 @@
         </is>
       </c>
       <c r="M821" s="2" t="n">
-        <v>3285.8</v>
+        <v>3232.78</v>
       </c>
     </row>
     <row r="822">
@@ -50605,7 +50605,7 @@
         </is>
       </c>
       <c r="M822" s="2" t="n">
-        <v>1152.09</v>
+        <v>1133.5</v>
       </c>
     </row>
     <row r="823">
@@ -50666,7 +50666,7 @@
         </is>
       </c>
       <c r="M823" s="2" t="n">
-        <v>1204.89</v>
+        <v>1185.45</v>
       </c>
     </row>
     <row r="824">
@@ -50727,7 +50727,7 @@
         </is>
       </c>
       <c r="M824" s="2" t="n">
-        <v>1052.24</v>
+        <v>1035.26</v>
       </c>
     </row>
     <row r="825">
@@ -50788,7 +50788,7 @@
         </is>
       </c>
       <c r="M825" s="2" t="n">
-        <v>7212.09</v>
+        <v>7095.71</v>
       </c>
     </row>
     <row r="826">
@@ -50849,7 +50849,7 @@
         </is>
       </c>
       <c r="M826" s="2" t="n">
-        <v>2505.38</v>
+        <v>2464.95</v>
       </c>
     </row>
     <row r="827">
@@ -50910,7 +50910,7 @@
         </is>
       </c>
       <c r="M827" s="2" t="n">
-        <v>783.2</v>
+        <v>770.5599999999999</v>
       </c>
     </row>
     <row r="828">
@@ -50971,7 +50971,7 @@
         </is>
       </c>
       <c r="M828" s="2" t="n">
-        <v>798.46</v>
+        <v>785.58</v>
       </c>
     </row>
     <row r="829">
@@ -51032,7 +51032,7 @@
         </is>
       </c>
       <c r="M829" s="2" t="n">
-        <v>2361.95</v>
+        <v>2323.84</v>
       </c>
     </row>
     <row r="830">
@@ -51093,7 +51093,7 @@
         </is>
       </c>
       <c r="M830" s="2" t="n">
-        <v>3792.28</v>
+        <v>3731.09</v>
       </c>
     </row>
     <row r="831">
@@ -51154,7 +51154,7 @@
         </is>
       </c>
       <c r="M831" s="2" t="n">
-        <v>5630.5</v>
+        <v>5539.64</v>
       </c>
     </row>
     <row r="832">
@@ -51215,7 +51215,7 @@
         </is>
       </c>
       <c r="M832" s="2" t="n">
-        <v>31994.14</v>
+        <v>31477.83</v>
       </c>
     </row>
     <row r="833">
@@ -51276,7 +51276,7 @@
         </is>
       </c>
       <c r="M833" s="2" t="n">
-        <v>1611.13</v>
+        <v>1585.13</v>
       </c>
     </row>
     <row r="834">
@@ -51337,7 +51337,7 @@
         </is>
       </c>
       <c r="M834" s="2" t="n">
-        <v>11902.94</v>
+        <v>11710.86</v>
       </c>
     </row>
     <row r="835">
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="M835" s="2" t="n">
-        <v>1705.58</v>
+        <v>1678.05</v>
       </c>
     </row>
     <row r="836">
@@ -51459,7 +51459,7 @@
         </is>
       </c>
       <c r="M836" s="2" t="n">
-        <v>3246.01</v>
+        <v>3193.63</v>
       </c>
     </row>
     <row r="837">
@@ -51520,7 +51520,7 @@
         </is>
       </c>
       <c r="M837" s="2" t="n">
-        <v>1340.02</v>
+        <v>1318.4</v>
       </c>
     </row>
     <row r="838">
@@ -51581,7 +51581,7 @@
         </is>
       </c>
       <c r="M838" s="2" t="n">
-        <v>2995.93</v>
+        <v>2947.58</v>
       </c>
     </row>
     <row r="839">
@@ -51642,7 +51642,7 @@
         </is>
       </c>
       <c r="M839" s="2" t="n">
-        <v>7400.99</v>
+        <v>7281.56</v>
       </c>
     </row>
     <row r="840">
@@ -51703,7 +51703,7 @@
         </is>
       </c>
       <c r="M840" s="2" t="n">
-        <v>1074.79</v>
+        <v>1057.45</v>
       </c>
     </row>
     <row r="841">
@@ -51764,7 +51764,7 @@
         </is>
       </c>
       <c r="M841" s="2" t="n">
-        <v>13059.49</v>
+        <v>12848.74</v>
       </c>
     </row>
     <row r="842">
@@ -51825,7 +51825,7 @@
         </is>
       </c>
       <c r="M842" s="2" t="n">
-        <v>8603.459999999999</v>
+        <v>8464.620000000001</v>
       </c>
     </row>
     <row r="843">
@@ -51886,7 +51886,7 @@
         </is>
       </c>
       <c r="M843" s="2" t="n">
-        <v>1343.15</v>
+        <v>1321.48</v>
       </c>
     </row>
     <row r="844">
@@ -51947,7 +51947,7 @@
         </is>
       </c>
       <c r="M844" s="2" t="n">
-        <v>3967.65</v>
+        <v>3903.62</v>
       </c>
     </row>
     <row r="845">
@@ -52008,7 +52008,7 @@
         </is>
       </c>
       <c r="M845" s="2" t="n">
-        <v>14265.12</v>
+        <v>14034.92</v>
       </c>
     </row>
     <row r="846">
@@ -52069,7 +52069,7 @@
         </is>
       </c>
       <c r="M846" s="2" t="n">
-        <v>8315.77</v>
+        <v>8181.57</v>
       </c>
     </row>
     <row r="847">
@@ -52130,7 +52130,7 @@
         </is>
       </c>
       <c r="M847" s="2" t="n">
-        <v>2453.75</v>
+        <v>2414.16</v>
       </c>
     </row>
     <row r="848">
@@ -52191,7 +52191,7 @@
         </is>
       </c>
       <c r="M848" s="2" t="n">
-        <v>1820.54</v>
+        <v>1791.16</v>
       </c>
     </row>
     <row r="849">
@@ -52252,7 +52252,7 @@
         </is>
       </c>
       <c r="M849" s="2" t="n">
-        <v>2511.36</v>
+        <v>2470.83</v>
       </c>
     </row>
     <row r="850">
@@ -52313,7 +52313,7 @@
         </is>
       </c>
       <c r="M850" s="2" t="n">
-        <v>6147.81</v>
+        <v>6048.6</v>
       </c>
     </row>
     <row r="851">
@@ -52374,7 +52374,7 @@
         </is>
       </c>
       <c r="M851" s="2" t="n">
-        <v>35032.79</v>
+        <v>34467.45</v>
       </c>
     </row>
     <row r="852">
@@ -52435,7 +52435,7 @@
         </is>
       </c>
       <c r="M852" s="2" t="n">
-        <v>6444.48</v>
+        <v>6340.48</v>
       </c>
     </row>
     <row r="853">
@@ -52496,7 +52496,7 @@
         </is>
       </c>
       <c r="M853" s="2" t="n">
-        <v>11174.41</v>
+        <v>10994.08</v>
       </c>
     </row>
     <row r="854">
@@ -52557,7 +52557,7 @@
         </is>
       </c>
       <c r="M854" s="2" t="n">
-        <v>2092.93</v>
+        <v>2059.16</v>
       </c>
     </row>
     <row r="855">
@@ -52618,7 +52618,7 @@
         </is>
       </c>
       <c r="M855" s="2" t="n">
-        <v>1454.74</v>
+        <v>1431.26</v>
       </c>
     </row>
     <row r="856">
@@ -52679,7 +52679,7 @@
         </is>
       </c>
       <c r="M856" s="2" t="n">
-        <v>4563.3</v>
+        <v>4489.66</v>
       </c>
     </row>
     <row r="857">
@@ -52740,7 +52740,7 @@
         </is>
       </c>
       <c r="M857" s="2" t="n">
-        <v>910.08</v>
+        <v>895.39</v>
       </c>
     </row>
     <row r="858">
@@ -52801,7 +52801,7 @@
         </is>
       </c>
       <c r="M858" s="2" t="n">
-        <v>1673.54</v>
+        <v>1646.54</v>
       </c>
     </row>
     <row r="859">
@@ -52862,7 +52862,7 @@
         </is>
       </c>
       <c r="M859" s="2" t="n">
-        <v>20538.76</v>
+        <v>20207.31</v>
       </c>
     </row>
     <row r="860">
@@ -52923,7 +52923,7 @@
         </is>
       </c>
       <c r="M860" s="2" t="n">
-        <v>1505.04</v>
+        <v>1480.76</v>
       </c>
     </row>
     <row r="861">
@@ -52984,7 +52984,7 @@
         </is>
       </c>
       <c r="M861" s="2" t="n">
-        <v>2704.96</v>
+        <v>2661.31</v>
       </c>
     </row>
     <row r="862">
@@ -53045,7 +53045,7 @@
         </is>
       </c>
       <c r="M862" s="2" t="n">
-        <v>934.9</v>
+        <v>919.8099999999999</v>
       </c>
     </row>
     <row r="863">
@@ -53106,7 +53106,7 @@
         </is>
       </c>
       <c r="M863" s="2" t="n">
-        <v>5624.68</v>
+        <v>5533.91</v>
       </c>
     </row>
     <row r="864">
@@ -53167,7 +53167,7 @@
         </is>
       </c>
       <c r="M864" s="2" t="n">
-        <v>10136</v>
+        <v>9972.42</v>
       </c>
     </row>
     <row r="865">
@@ -53228,7 +53228,7 @@
         </is>
       </c>
       <c r="M865" s="2" t="n">
-        <v>2799.84</v>
+        <v>2754.66</v>
       </c>
     </row>
     <row r="866">
@@ -53289,7 +53289,7 @@
         </is>
       </c>
       <c r="M866" s="2" t="n">
-        <v>6727.23</v>
+        <v>6618.67</v>
       </c>
     </row>
     <row r="867">
@@ -53350,7 +53350,7 @@
         </is>
       </c>
       <c r="M867" s="2" t="n">
-        <v>8268.309999999999</v>
+        <v>8135.74</v>
       </c>
     </row>
     <row r="868">
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="M868" s="2" t="n">
-        <v>795.04</v>
+        <v>782.3</v>
       </c>
     </row>
     <row r="869">
@@ -53472,7 +53472,7 @@
         </is>
       </c>
       <c r="M869" s="2" t="n">
-        <v>2528.67</v>
+        <v>2488.13</v>
       </c>
     </row>
     <row r="870">
@@ -53533,7 +53533,7 @@
         </is>
       </c>
       <c r="M870" s="2" t="n">
-        <v>32901.81</v>
+        <v>32374.28</v>
       </c>
     </row>
     <row r="871">
@@ -53594,7 +53594,7 @@
         </is>
       </c>
       <c r="M871" s="2" t="n">
-        <v>10179.88</v>
+        <v>10016.66</v>
       </c>
     </row>
     <row r="872">
@@ -53655,7 +53655,7 @@
         </is>
       </c>
       <c r="M872" s="2" t="n">
-        <v>3642.79</v>
+        <v>3584.39</v>
       </c>
     </row>
     <row r="873">
@@ -53716,7 +53716,7 @@
         </is>
       </c>
       <c r="M873" s="2" t="n">
-        <v>1155.53</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="874">
@@ -53777,7 +53777,7 @@
         </is>
       </c>
       <c r="M874" s="2" t="n">
-        <v>13663.58</v>
+        <v>13444.5</v>
       </c>
     </row>
     <row r="875">
@@ -53838,7 +53838,7 @@
         </is>
       </c>
       <c r="M875" s="2" t="n">
-        <v>1231.98</v>
+        <v>1212.22</v>
       </c>
     </row>
     <row r="876">
@@ -53899,7 +53899,7 @@
         </is>
       </c>
       <c r="M876" s="2" t="n">
-        <v>13807.66</v>
+        <v>13586.28</v>
       </c>
     </row>
     <row r="877">
@@ -53960,7 +53960,7 @@
         </is>
       </c>
       <c r="M877" s="2" t="n">
-        <v>1550.47</v>
+        <v>1525.61</v>
       </c>
     </row>
     <row r="878">
@@ -54021,7 +54021,7 @@
         </is>
       </c>
       <c r="M878" s="2" t="n">
-        <v>2692.8</v>
+        <v>2649.63</v>
       </c>
     </row>
     <row r="879">
@@ -54082,7 +54082,7 @@
         </is>
       </c>
       <c r="M879" s="2" t="n">
-        <v>1239.89</v>
+        <v>1220.01</v>
       </c>
     </row>
     <row r="880">
@@ -54143,7 +54143,7 @@
         </is>
       </c>
       <c r="M880" s="2" t="n">
-        <v>3580.21</v>
+        <v>3522.81</v>
       </c>
     </row>
     <row r="881">
@@ -54204,7 +54204,7 @@
         </is>
       </c>
       <c r="M881" s="2" t="n">
-        <v>6547.14</v>
+        <v>6442.17</v>
       </c>
     </row>
     <row r="882">
@@ -54265,7 +54265,7 @@
         </is>
       </c>
       <c r="M882" s="2" t="n">
-        <v>4240.98</v>
+        <v>4172.99</v>
       </c>
     </row>
     <row r="883">
@@ -54326,7 +54326,7 @@
         </is>
       </c>
       <c r="M883" s="2" t="n">
-        <v>2576.59</v>
+        <v>2535.28</v>
       </c>
     </row>
     <row r="884">
@@ -54387,7 +54387,7 @@
         </is>
       </c>
       <c r="M884" s="2" t="n">
-        <v>13638.79</v>
+        <v>13420.11</v>
       </c>
     </row>
     <row r="885">
@@ -54448,7 +54448,7 @@
         </is>
       </c>
       <c r="M885" s="2" t="n">
-        <v>1229.02</v>
+        <v>1209.32</v>
       </c>
     </row>
     <row r="886">
@@ -54509,7 +54509,7 @@
         </is>
       </c>
       <c r="M886" s="2" t="n">
-        <v>1617.5</v>
+        <v>1591.57</v>
       </c>
     </row>
     <row r="887">
@@ -54570,7 +54570,7 @@
         </is>
       </c>
       <c r="M887" s="2" t="n">
-        <v>2322.2</v>
+        <v>2284.97</v>
       </c>
     </row>
     <row r="888">
@@ -54631,7 +54631,7 @@
         </is>
       </c>
       <c r="M888" s="2" t="n">
-        <v>1146.13</v>
+        <v>1127.75</v>
       </c>
     </row>
     <row r="889">
@@ -54692,7 +54692,7 @@
         </is>
       </c>
       <c r="M889" s="2" t="n">
-        <v>6009.69</v>
+        <v>5913.33</v>
       </c>
     </row>
     <row r="890">
@@ -54753,7 +54753,7 @@
         </is>
       </c>
       <c r="M890" s="2" t="n">
-        <v>11335.65</v>
+        <v>11153.89</v>
       </c>
     </row>
     <row r="891">
@@ -54814,7 +54814,7 @@
         </is>
       </c>
       <c r="M891" s="2" t="n">
-        <v>55169.21</v>
+        <v>54284.65</v>
       </c>
     </row>
     <row r="892">
@@ -54875,7 +54875,7 @@
         </is>
       </c>
       <c r="M892" s="2" t="n">
-        <v>11517.94</v>
+        <v>11333.26</v>
       </c>
     </row>
     <row r="893">
@@ -54936,7 +54936,7 @@
         </is>
       </c>
       <c r="M893" s="2" t="n">
-        <v>9309.219999999999</v>
+        <v>9159.959999999999</v>
       </c>
     </row>
     <row r="894">
@@ -54997,7 +54997,7 @@
         </is>
       </c>
       <c r="M894" s="2" t="n">
-        <v>1610.87</v>
+        <v>1585.04</v>
       </c>
     </row>
     <row r="895">
@@ -55058,7 +55058,7 @@
         </is>
       </c>
       <c r="M895" s="2" t="n">
-        <v>2080.33</v>
+        <v>2046.98</v>
       </c>
     </row>
     <row r="896">
@@ -55119,7 +55119,7 @@
         </is>
       </c>
       <c r="M896" s="2" t="n">
-        <v>806.42</v>
+        <v>793.49</v>
       </c>
     </row>
     <row r="897">
@@ -55180,7 +55180,7 @@
         </is>
       </c>
       <c r="M897" s="2" t="n">
-        <v>1004.21</v>
+        <v>988.11</v>
       </c>
     </row>
     <row r="898">
@@ -55241,7 +55241,7 @@
         </is>
       </c>
       <c r="M898" s="2" t="n">
-        <v>38493.97</v>
+        <v>37876.77</v>
       </c>
     </row>
     <row r="899">
@@ -55302,7 +55302,7 @@
         </is>
       </c>
       <c r="M899" s="2" t="n">
-        <v>780.25</v>
+        <v>767.74</v>
       </c>
     </row>
     <row r="900">
@@ -55363,7 +55363,7 @@
         </is>
       </c>
       <c r="M900" s="2" t="n">
-        <v>7119.98</v>
+        <v>7005.82</v>
       </c>
     </row>
     <row r="901">
@@ -55424,7 +55424,7 @@
         </is>
       </c>
       <c r="M901" s="2" t="n">
-        <v>69412.89</v>
+        <v>68299.95</v>
       </c>
     </row>
     <row r="902">
@@ -55485,7 +55485,7 @@
         </is>
       </c>
       <c r="M902" s="2" t="n">
-        <v>2240.63</v>
+        <v>2204.71</v>
       </c>
     </row>
     <row r="903">
@@ -55546,7 +55546,7 @@
         </is>
       </c>
       <c r="M903" s="2" t="n">
-        <v>2306.72</v>
+        <v>2269.74</v>
       </c>
     </row>
     <row r="904">
@@ -55607,7 +55607,7 @@
         </is>
       </c>
       <c r="M904" s="2" t="n">
-        <v>3507.49</v>
+        <v>3451.26</v>
       </c>
     </row>
     <row r="905">
@@ -55668,7 +55668,7 @@
         </is>
       </c>
       <c r="M905" s="2" t="n">
-        <v>16149.05</v>
+        <v>15890.12</v>
       </c>
     </row>
     <row r="906">
@@ -55729,7 +55729,7 @@
         </is>
       </c>
       <c r="M906" s="2" t="n">
-        <v>775.6</v>
+        <v>763.17</v>
       </c>
     </row>
     <row r="907">
@@ -55790,7 +55790,7 @@
         </is>
       </c>
       <c r="M907" s="2" t="n">
-        <v>1134.18</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="908">
@@ -55851,7 +55851,7 @@
         </is>
       </c>
       <c r="M908" s="2" t="n">
-        <v>14633.25</v>
+        <v>14398.63</v>
       </c>
     </row>
     <row r="909">
@@ -55912,7 +55912,7 @@
         </is>
       </c>
       <c r="M909" s="2" t="n">
-        <v>42070.6</v>
+        <v>41396.06</v>
       </c>
     </row>
     <row r="910">
@@ -55973,7 +55973,7 @@
         </is>
       </c>
       <c r="M910" s="2" t="n">
-        <v>2551.66</v>
+        <v>2521.97</v>
       </c>
     </row>
     <row r="911">
@@ -56034,7 +56034,7 @@
         </is>
       </c>
       <c r="M911" s="2" t="n">
-        <v>2289.06</v>
+        <v>2262.43</v>
       </c>
     </row>
     <row r="912">
@@ -56095,7 +56095,7 @@
         </is>
       </c>
       <c r="M912" s="2" t="n">
-        <v>931.48</v>
+        <v>920.64</v>
       </c>
     </row>
     <row r="913">
@@ -56156,7 +56156,7 @@
         </is>
       </c>
       <c r="M913" s="2" t="n">
-        <v>2334.25</v>
+        <v>2307.09</v>
       </c>
     </row>
     <row r="914">
@@ -56217,7 +56217,7 @@
         </is>
       </c>
       <c r="M914" s="2" t="n">
-        <v>967.98</v>
+        <v>956.72</v>
       </c>
     </row>
     <row r="915">
@@ -56278,7 +56278,7 @@
         </is>
       </c>
       <c r="M915" s="2" t="n">
-        <v>3602.94</v>
+        <v>3561.02</v>
       </c>
     </row>
     <row r="916">
@@ -56339,7 +56339,7 @@
         </is>
       </c>
       <c r="M916" s="2" t="n">
-        <v>3158.54</v>
+        <v>3121.78</v>
       </c>
     </row>
     <row r="917">
@@ -56400,7 +56400,7 @@
         </is>
       </c>
       <c r="M917" s="2" t="n">
-        <v>5387.74</v>
+        <v>5325.05</v>
       </c>
     </row>
     <row r="918">
@@ -56461,7 +56461,7 @@
         </is>
       </c>
       <c r="M918" s="2" t="n">
-        <v>780.9400000000001</v>
+        <v>771.85</v>
       </c>
     </row>
     <row r="919">
@@ -56522,7 +56522,7 @@
         </is>
       </c>
       <c r="M919" s="2" t="n">
-        <v>1174.19</v>
+        <v>1160.53</v>
       </c>
     </row>
     <row r="920">
@@ -56583,7 +56583,7 @@
         </is>
       </c>
       <c r="M920" s="2" t="n">
-        <v>4364.59</v>
+        <v>4313.81</v>
       </c>
     </row>
     <row r="921">
@@ -56644,7 +56644,7 @@
         </is>
       </c>
       <c r="M921" s="2" t="n">
-        <v>2355.36</v>
+        <v>2327.95</v>
       </c>
     </row>
     <row r="922">
@@ -56705,7 +56705,7 @@
         </is>
       </c>
       <c r="M922" s="2" t="n">
-        <v>4405.93</v>
+        <v>4354.66</v>
       </c>
     </row>
     <row r="923">
@@ -56766,7 +56766,7 @@
         </is>
       </c>
       <c r="M923" s="2" t="n">
-        <v>1664.6</v>
+        <v>1645.23</v>
       </c>
     </row>
     <row r="924">
@@ -56827,7 +56827,7 @@
         </is>
       </c>
       <c r="M924" s="2" t="n">
-        <v>773.5</v>
+        <v>764.5</v>
       </c>
     </row>
     <row r="925">
@@ -56888,7 +56888,7 @@
         </is>
       </c>
       <c r="M925" s="2" t="n">
-        <v>5892.47</v>
+        <v>5823.91</v>
       </c>
     </row>
     <row r="926">
@@ -56949,7 +56949,7 @@
         </is>
       </c>
       <c r="M926" s="2" t="n">
-        <v>2715.36</v>
+        <v>2683.76</v>
       </c>
     </row>
     <row r="927">
@@ -57010,7 +57010,7 @@
         </is>
       </c>
       <c r="M927" s="2" t="n">
-        <v>2778.5</v>
+        <v>2746.17</v>
       </c>
     </row>
     <row r="928">
@@ -57071,7 +57071,7 @@
         </is>
       </c>
       <c r="M928" s="2" t="n">
-        <v>1049.69</v>
+        <v>1037.47</v>
       </c>
     </row>
     <row r="929">
@@ -57132,7 +57132,7 @@
         </is>
       </c>
       <c r="M929" s="2" t="n">
-        <v>5585.89</v>
+        <v>5520.9</v>
       </c>
     </row>
     <row r="930">
@@ -57193,7 +57193,7 @@
         </is>
       </c>
       <c r="M930" s="2" t="n">
-        <v>1395.92</v>
+        <v>1379.68</v>
       </c>
     </row>
     <row r="931">
@@ -57254,7 +57254,7 @@
         </is>
       </c>
       <c r="M931" s="2" t="n">
-        <v>6066.09</v>
+        <v>5995.51</v>
       </c>
     </row>
     <row r="932">
@@ -57315,7 +57315,7 @@
         </is>
       </c>
       <c r="M932" s="2" t="n">
-        <v>1100.4</v>
+        <v>1087.6</v>
       </c>
     </row>
     <row r="933">
@@ -57376,7 +57376,7 @@
         </is>
       </c>
       <c r="M933" s="2" t="n">
-        <v>922.29</v>
+        <v>911.5599999999999</v>
       </c>
     </row>
     <row r="934">
@@ -57437,7 +57437,7 @@
         </is>
       </c>
       <c r="M934" s="2" t="n">
-        <v>908.23</v>
+        <v>897.66</v>
       </c>
     </row>
     <row r="935">
@@ -57498,7 +57498,7 @@
         </is>
       </c>
       <c r="M935" s="2" t="n">
-        <v>1569.89</v>
+        <v>1551.63</v>
       </c>
     </row>
     <row r="936">
@@ -57559,7 +57559,7 @@
         </is>
       </c>
       <c r="M936" s="2" t="n">
-        <v>6468.4</v>
+        <v>6393.13</v>
       </c>
     </row>
     <row r="937">
@@ -57620,7 +57620,7 @@
         </is>
       </c>
       <c r="M937" s="2" t="n">
-        <v>2193.32</v>
+        <v>2167.8</v>
       </c>
     </row>
     <row r="938">
@@ -57681,7 +57681,7 @@
         </is>
       </c>
       <c r="M938" s="2" t="n">
-        <v>3434.29</v>
+        <v>3394.33</v>
       </c>
     </row>
     <row r="939">
@@ -57742,7 +57742,7 @@
         </is>
       </c>
       <c r="M939" s="2" t="n">
-        <v>1622.85</v>
+        <v>1603.97</v>
       </c>
     </row>
     <row r="940">
@@ -57803,7 +57803,7 @@
         </is>
       </c>
       <c r="M940" s="2" t="n">
-        <v>1628.43</v>
+        <v>1609.48</v>
       </c>
     </row>
     <row r="941">
@@ -57864,7 +57864,7 @@
         </is>
       </c>
       <c r="M941" s="2" t="n">
-        <v>1172.27</v>
+        <v>1158.63</v>
       </c>
     </row>
     <row r="942">
@@ -57925,7 +57925,7 @@
         </is>
       </c>
       <c r="M942" s="2" t="n">
-        <v>2341.01</v>
+        <v>2313.77</v>
       </c>
     </row>
     <row r="943">
@@ -57986,7 +57986,7 @@
         </is>
       </c>
       <c r="M943" s="2" t="n">
-        <v>1362.96</v>
+        <v>1347.1</v>
       </c>
     </row>
     <row r="944">
@@ -58047,7 +58047,7 @@
         </is>
       </c>
       <c r="M944" s="2" t="n">
-        <v>6788.38</v>
+        <v>6709.4</v>
       </c>
     </row>
     <row r="945">
@@ -58108,7 +58108,7 @@
         </is>
       </c>
       <c r="M945" s="2" t="n">
-        <v>1443.41</v>
+        <v>1426.62</v>
       </c>
     </row>
     <row r="946">
@@ -58169,7 +58169,7 @@
         </is>
       </c>
       <c r="M946" s="2" t="n">
-        <v>871.14</v>
+        <v>861.01</v>
       </c>
     </row>
     <row r="947">
@@ -58230,7 +58230,7 @@
         </is>
       </c>
       <c r="M947" s="2" t="n">
-        <v>1682.59</v>
+        <v>1663.02</v>
       </c>
     </row>
     <row r="948">
@@ -58291,7 +58291,7 @@
         </is>
       </c>
       <c r="M948" s="2" t="n">
-        <v>3684.19</v>
+        <v>3641.32</v>
       </c>
     </row>
     <row r="949">
@@ -58352,7 +58352,7 @@
         </is>
       </c>
       <c r="M949" s="2" t="n">
-        <v>1131.24</v>
+        <v>1118.08</v>
       </c>
     </row>
     <row r="950">
@@ -58413,7 +58413,7 @@
         </is>
       </c>
       <c r="M950" s="2" t="n">
-        <v>5891.99</v>
+        <v>5823.43</v>
       </c>
     </row>
     <row r="951">
@@ -58474,7 +58474,7 @@
         </is>
       </c>
       <c r="M951" s="2" t="n">
-        <v>1177.41</v>
+        <v>1163.71</v>
       </c>
     </row>
     <row r="952">
@@ -58535,7 +58535,7 @@
         </is>
       </c>
       <c r="M952" s="2" t="n">
-        <v>9423.16</v>
+        <v>9313.52</v>
       </c>
     </row>
     <row r="953">
@@ -58596,7 +58596,7 @@
         </is>
       </c>
       <c r="M953" s="2" t="n">
-        <v>2372.09</v>
+        <v>2344.49</v>
       </c>
     </row>
     <row r="954">
@@ -58657,7 +58657,7 @@
         </is>
       </c>
       <c r="M954" s="2" t="n">
-        <v>776.86</v>
+        <v>767.8200000000001</v>
       </c>
     </row>
     <row r="955">
@@ -58718,7 +58718,7 @@
         </is>
       </c>
       <c r="M955" s="2" t="n">
-        <v>1309.76</v>
+        <v>1294.52</v>
       </c>
     </row>
     <row r="956">
@@ -58779,7 +58779,7 @@
         </is>
       </c>
       <c r="M956" s="2" t="n">
-        <v>4161.98</v>
+        <v>4113.55</v>
       </c>
     </row>
     <row r="957">
@@ -58840,7 +58840,7 @@
         </is>
       </c>
       <c r="M957" s="2" t="n">
-        <v>1172.45</v>
+        <v>1158.81</v>
       </c>
     </row>
     <row r="958">
@@ -58901,7 +58901,7 @@
         </is>
       </c>
       <c r="M958" s="2" t="n">
-        <v>868.66</v>
+        <v>858.5599999999999</v>
       </c>
     </row>
     <row r="959">
@@ -58962,7 +58962,7 @@
         </is>
       </c>
       <c r="M959" s="2" t="n">
-        <v>6160.93</v>
+        <v>6089.25</v>
       </c>
     </row>
     <row r="960">
@@ -59023,7 +59023,7 @@
         </is>
       </c>
       <c r="M960" s="2" t="n">
-        <v>3503.09</v>
+        <v>3462.33</v>
       </c>
     </row>
     <row r="961">
@@ -59084,7 +59084,7 @@
         </is>
       </c>
       <c r="M961" s="2" t="n">
-        <v>1470.97</v>
+        <v>1453.85</v>
       </c>
     </row>
     <row r="962">
@@ -59145,7 +59145,7 @@
         </is>
       </c>
       <c r="M962" s="2" t="n">
-        <v>12727.84</v>
+        <v>12579.75</v>
       </c>
     </row>
     <row r="963">
@@ -59206,7 +59206,7 @@
         </is>
       </c>
       <c r="M963" s="2" t="n">
-        <v>6018.19</v>
+        <v>5948.17</v>
       </c>
     </row>
     <row r="964">
@@ -59267,7 +59267,7 @@
         </is>
       </c>
       <c r="M964" s="2" t="n">
-        <v>1740.87</v>
+        <v>1720.61</v>
       </c>
     </row>
     <row r="965">
@@ -59328,7 +59328,7 @@
         </is>
       </c>
       <c r="M965" s="2" t="n">
-        <v>11517.87</v>
+        <v>11383.86</v>
       </c>
     </row>
     <row r="966">
@@ -59389,7 +59389,7 @@
         </is>
       </c>
       <c r="M966" s="2" t="n">
-        <v>2248.42</v>
+        <v>2235.95</v>
       </c>
     </row>
     <row r="967">
@@ -59450,7 +59450,7 @@
         </is>
       </c>
       <c r="M967" s="2" t="n">
-        <v>12757.31</v>
+        <v>12686.59</v>
       </c>
     </row>
     <row r="968">
@@ -59511,7 +59511,7 @@
         </is>
       </c>
       <c r="M968" s="2" t="n">
-        <v>1064.43</v>
+        <v>1058.52</v>
       </c>
     </row>
     <row r="969">
@@ -59572,7 +59572,7 @@
         </is>
       </c>
       <c r="M969" s="2" t="n">
-        <v>3664.88</v>
+        <v>3644.56</v>
       </c>
     </row>
     <row r="970">
@@ -59633,7 +59633,7 @@
         </is>
       </c>
       <c r="M970" s="2" t="n">
-        <v>3838.54</v>
+        <v>3817.26</v>
       </c>
     </row>
     <row r="971">
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="M971" s="2" t="n">
-        <v>1754.57</v>
+        <v>1744.84</v>
       </c>
     </row>
     <row r="972">
@@ -59755,7 +59755,7 @@
         </is>
       </c>
       <c r="M972" s="2" t="n">
-        <v>2392.86</v>
+        <v>2379.59</v>
       </c>
     </row>
     <row r="973">
@@ -59816,7 +59816,7 @@
         </is>
       </c>
       <c r="M973" s="2" t="n">
-        <v>4361.79</v>
+        <v>4337.61</v>
       </c>
     </row>
     <row r="974">
@@ -59877,7 +59877,7 @@
         </is>
       </c>
       <c r="M974" s="2" t="n">
-        <v>15495.63</v>
+        <v>15409.73</v>
       </c>
     </row>
     <row r="975">
@@ -59938,7 +59938,7 @@
         </is>
       </c>
       <c r="M975" s="2" t="n">
-        <v>2164.01</v>
+        <v>2152.01</v>
       </c>
     </row>
     <row r="976">
@@ -59999,7 +59999,7 @@
         </is>
       </c>
       <c r="M976" s="2" t="n">
-        <v>7418.63</v>
+        <v>7377.5</v>
       </c>
     </row>
     <row r="977">
@@ -60060,7 +60060,7 @@
         </is>
       </c>
       <c r="M977" s="2" t="n">
-        <v>859.51</v>
+        <v>854.75</v>
       </c>
     </row>
     <row r="978">
@@ -60121,7 +60121,7 @@
         </is>
       </c>
       <c r="M978" s="2" t="n">
-        <v>1069.63</v>
+        <v>1063.7</v>
       </c>
     </row>
     <row r="979">
@@ -60182,7 +60182,7 @@
         </is>
       </c>
       <c r="M979" s="2" t="n">
-        <v>4105.85</v>
+        <v>4083.08</v>
       </c>
     </row>
     <row r="980">
@@ -60243,7 +60243,7 @@
         </is>
       </c>
       <c r="M980" s="2" t="n">
-        <v>26086.25</v>
+        <v>25941.63</v>
       </c>
     </row>
     <row r="981">
@@ -60304,7 +60304,7 @@
         </is>
       </c>
       <c r="M981" s="2" t="n">
-        <v>33131.39</v>
+        <v>32947.71</v>
       </c>
     </row>
     <row r="982">
@@ -60365,7 +60365,7 @@
         </is>
       </c>
       <c r="M982" s="2" t="n">
-        <v>2380.08</v>
+        <v>2366.88</v>
       </c>
     </row>
     <row r="983">
@@ -60426,7 +60426,7 @@
         </is>
       </c>
       <c r="M983" s="2" t="n">
-        <v>829.01</v>
+        <v>824.42</v>
       </c>
     </row>
     <row r="984">
@@ -60487,7 +60487,7 @@
         </is>
       </c>
       <c r="M984" s="2" t="n">
-        <v>3360.16</v>
+        <v>3341.54</v>
       </c>
     </row>
     <row r="985">
@@ -60548,7 +60548,7 @@
         </is>
       </c>
       <c r="M985" s="2" t="n">
-        <v>3272.44</v>
+        <v>3254.3</v>
       </c>
     </row>
     <row r="986">
@@ -60609,7 +60609,7 @@
         </is>
       </c>
       <c r="M986" s="2" t="n">
-        <v>15935.98</v>
+        <v>15847.63</v>
       </c>
     </row>
     <row r="987">
@@ -60670,7 +60670,7 @@
         </is>
       </c>
       <c r="M987" s="2" t="n">
-        <v>964.1900000000001</v>
+        <v>958.85</v>
       </c>
     </row>
     <row r="988">
@@ -60731,7 +60731,7 @@
         </is>
       </c>
       <c r="M988" s="2" t="n">
-        <v>1040.48</v>
+        <v>1034.72</v>
       </c>
     </row>
     <row r="989">
@@ -60792,7 +60792,7 @@
         </is>
       </c>
       <c r="M989" s="2" t="n">
-        <v>1793.87</v>
+        <v>1783.92</v>
       </c>
     </row>
     <row r="990">
@@ -60853,7 +60853,7 @@
         </is>
       </c>
       <c r="M990" s="2" t="n">
-        <v>2438.54</v>
+        <v>2425.02</v>
       </c>
     </row>
     <row r="991">
@@ -60918,7 +60918,7 @@
         </is>
       </c>
       <c r="M991" s="2" t="n">
-        <v>81195.69</v>
+        <v>80745.55</v>
       </c>
     </row>
     <row r="992">
@@ -60979,7 +60979,7 @@
         </is>
       </c>
       <c r="M992" s="2" t="n">
-        <v>1072.96</v>
+        <v>1067.02</v>
       </c>
     </row>
     <row r="993">
@@ -61040,7 +61040,7 @@
         </is>
       </c>
       <c r="M993" s="2" t="n">
-        <v>2698.91</v>
+        <v>2683.95</v>
       </c>
     </row>
     <row r="994">
@@ -61101,7 +61101,7 @@
         </is>
       </c>
       <c r="M994" s="2" t="n">
-        <v>1391.5</v>
+        <v>1383.79</v>
       </c>
     </row>
     <row r="995">
@@ -61162,7 +61162,7 @@
         </is>
       </c>
       <c r="M995" s="2" t="n">
-        <v>1180.01</v>
+        <v>1173.47</v>
       </c>
     </row>
     <row r="996">
@@ -61223,7 +61223,7 @@
         </is>
       </c>
       <c r="M996" s="2" t="n">
-        <v>945.1</v>
+        <v>939.86</v>
       </c>
     </row>
     <row r="997">
@@ -61284,7 +61284,7 @@
         </is>
       </c>
       <c r="M997" s="2" t="n">
-        <v>12950.6</v>
+        <v>12878.8</v>
       </c>
     </row>
     <row r="998">
@@ -61345,7 +61345,7 @@
         </is>
       </c>
       <c r="M998" s="2" t="n">
-        <v>1743.68</v>
+        <v>1734.01</v>
       </c>
     </row>
     <row r="999">
@@ -61406,7 +61406,7 @@
         </is>
       </c>
       <c r="M999" s="2" t="n">
-        <v>1125.72</v>
+        <v>1119.48</v>
       </c>
     </row>
     <row r="1000">
@@ -61467,7 +61467,7 @@
         </is>
       </c>
       <c r="M1000" s="2" t="n">
-        <v>1197.45</v>
+        <v>1190.81</v>
       </c>
     </row>
     <row r="1001">
@@ -61528,7 +61528,7 @@
         </is>
       </c>
       <c r="M1001" s="2" t="n">
-        <v>1611.22</v>
+        <v>1602.28</v>
       </c>
     </row>
     <row r="1002">
@@ -61589,7 +61589,7 @@
         </is>
       </c>
       <c r="M1002" s="2" t="n">
-        <v>2943.5</v>
+        <v>2927.18</v>
       </c>
     </row>
     <row r="1003">
@@ -61650,7 +61650,7 @@
         </is>
       </c>
       <c r="M1003" s="2" t="n">
-        <v>12084.59</v>
+        <v>12017.59</v>
       </c>
     </row>
     <row r="1004">
@@ -61711,7 +61711,7 @@
         </is>
       </c>
       <c r="M1004" s="2" t="n">
-        <v>1662.85</v>
+        <v>1653.63</v>
       </c>
     </row>
     <row r="1005">
@@ -61772,7 +61772,7 @@
         </is>
       </c>
       <c r="M1005" s="2" t="n">
-        <v>3080.07</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1006">
@@ -61833,7 +61833,7 @@
         </is>
       </c>
       <c r="M1006" s="2" t="n">
-        <v>2512.86</v>
+        <v>2498.93</v>
       </c>
     </row>
     <row r="1007">
@@ -61894,7 +61894,7 @@
         </is>
       </c>
       <c r="M1007" s="2" t="n">
-        <v>831.83</v>
+        <v>827.21</v>
       </c>
     </row>
     <row r="1008">
@@ -61955,7 +61955,7 @@
         </is>
       </c>
       <c r="M1008" s="2" t="n">
-        <v>1494.99</v>
+        <v>1486.7</v>
       </c>
     </row>
     <row r="1009">
@@ -62016,7 +62016,7 @@
         </is>
       </c>
       <c r="M1009" s="2" t="n">
-        <v>1218.59</v>
+        <v>1211.83</v>
       </c>
     </row>
     <row r="1010">
@@ -62077,7 +62077,7 @@
         </is>
       </c>
       <c r="M1010" s="2" t="n">
-        <v>2077.13</v>
+        <v>2065.62</v>
       </c>
     </row>
     <row r="1011">
@@ -62138,7 +62138,7 @@
         </is>
       </c>
       <c r="M1011" s="2" t="n">
-        <v>1366.29</v>
+        <v>1358.72</v>
       </c>
     </row>
     <row r="1012">
@@ -62199,7 +62199,7 @@
         </is>
       </c>
       <c r="M1012" s="2" t="n">
-        <v>13435.35</v>
+        <v>13360.86</v>
       </c>
     </row>
     <row r="1013">
@@ -62260,7 +62260,7 @@
         </is>
       </c>
       <c r="M1013" s="2" t="n">
-        <v>1773.17</v>
+        <v>1764.45</v>
       </c>
     </row>
     <row r="1014">
@@ -62321,7 +62321,7 @@
         </is>
       </c>
       <c r="M1014" s="2" t="n">
-        <v>14437.5</v>
+        <v>14366.51</v>
       </c>
     </row>
     <row r="1015">
@@ -62382,7 +62382,7 @@
         </is>
       </c>
       <c r="M1015" s="2" t="n">
-        <v>3739</v>
+        <v>3720.61</v>
       </c>
     </row>
     <row r="1016">
@@ -62443,7 +62443,7 @@
         </is>
       </c>
       <c r="M1016" s="2" t="n">
-        <v>1603.21</v>
+        <v>1595.33</v>
       </c>
     </row>
     <row r="1017">
@@ -62504,7 +62504,7 @@
         </is>
       </c>
       <c r="M1017" s="2" t="n">
-        <v>4877.75</v>
+        <v>4853.77</v>
       </c>
     </row>
     <row r="1018">
@@ -62565,7 +62565,7 @@
         </is>
       </c>
       <c r="M1018" s="2" t="n">
-        <v>794.3099999999999</v>
+        <v>790.41</v>
       </c>
     </row>
     <row r="1019">
@@ -62626,7 +62626,7 @@
         </is>
       </c>
       <c r="M1019" s="2" t="n">
-        <v>2263.25</v>
+        <v>2252.12</v>
       </c>
     </row>
     <row r="1020">
@@ -62687,7 +62687,7 @@
         </is>
       </c>
       <c r="M1020" s="2" t="n">
-        <v>2235.97</v>
+        <v>2224.97</v>
       </c>
     </row>
     <row r="1021">
@@ -62748,7 +62748,7 @@
         </is>
       </c>
       <c r="M1021" s="2" t="n">
-        <v>806.4400000000001</v>
+        <v>802.47</v>
       </c>
     </row>
     <row r="1022">
@@ -62809,7 +62809,7 @@
         </is>
       </c>
       <c r="M1022" s="2" t="n">
-        <v>6197.27</v>
+        <v>6166.8</v>
       </c>
     </row>
     <row r="1023">
@@ -62870,7 +62870,7 @@
         </is>
       </c>
       <c r="M1023" s="2" t="n">
-        <v>2329.59</v>
+        <v>2318.13</v>
       </c>
     </row>
     <row r="1024">
@@ -62931,7 +62931,7 @@
         </is>
       </c>
       <c r="M1024" s="2" t="n">
-        <v>2186.12</v>
+        <v>2175.37</v>
       </c>
     </row>
     <row r="1025">
@@ -62992,7 +62992,7 @@
         </is>
       </c>
       <c r="M1025" s="2" t="n">
-        <v>877.37</v>
+        <v>873.0599999999999</v>
       </c>
     </row>
     <row r="1026">
@@ -63053,7 +63053,7 @@
         </is>
       </c>
       <c r="M1026" s="2" t="n">
-        <v>1767.21</v>
+        <v>1758.52</v>
       </c>
     </row>
     <row r="1027">
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="M1027" s="2" t="n">
-        <v>3919.6</v>
+        <v>3900.33</v>
       </c>
     </row>
     <row r="1028">
@@ -63175,7 +63175,7 @@
         </is>
       </c>
       <c r="M1028" s="2" t="n">
-        <v>5777.99</v>
+        <v>5749.58</v>
       </c>
     </row>
     <row r="1029">
@@ -63236,7 +63236,7 @@
         </is>
       </c>
       <c r="M1029" s="2" t="n">
-        <v>2967.61</v>
+        <v>2953.02</v>
       </c>
     </row>
     <row r="1030">
@@ -63297,7 +63297,7 @@
         </is>
       </c>
       <c r="M1030" s="2" t="n">
-        <v>1677.6</v>
+        <v>1669.36</v>
       </c>
     </row>
     <row r="1031">
@@ -63358,7 +63358,7 @@
         </is>
       </c>
       <c r="M1031" s="2" t="n">
-        <v>2646.08</v>
+        <v>2633.07</v>
       </c>
     </row>
     <row r="1032">
@@ -63419,7 +63419,7 @@
         </is>
       </c>
       <c r="M1032" s="2" t="n">
-        <v>2501.89</v>
+        <v>2489.59</v>
       </c>
     </row>
     <row r="1033">
@@ -63480,7 +63480,7 @@
         </is>
       </c>
       <c r="M1033" s="2" t="n">
-        <v>18442.65</v>
+        <v>18351.98</v>
       </c>
     </row>
     <row r="1034">
@@ -63541,7 +63541,7 @@
         </is>
       </c>
       <c r="M1034" s="2" t="n">
-        <v>14611.55</v>
+        <v>14539.71</v>
       </c>
     </row>
     <row r="1035">
@@ -63602,7 +63602,7 @@
         </is>
       </c>
       <c r="M1035" s="2" t="n">
-        <v>1551.2</v>
+        <v>1543.57</v>
       </c>
     </row>
     <row r="1036">
@@ -63663,7 +63663,7 @@
         </is>
       </c>
       <c r="M1036" s="2" t="n">
-        <v>3536.05</v>
+        <v>3518.66</v>
       </c>
     </row>
     <row r="1037">
@@ -63724,7 +63724,7 @@
         </is>
       </c>
       <c r="M1037" s="2" t="n">
-        <v>4975.05</v>
+        <v>4950.59</v>
       </c>
     </row>
     <row r="1038">
@@ -63785,7 +63785,7 @@
         </is>
       </c>
       <c r="M1038" s="2" t="n">
-        <v>2146.99</v>
+        <v>2136.44</v>
       </c>
     </row>
     <row r="1039">
@@ -63846,7 +63846,7 @@
         </is>
       </c>
       <c r="M1039" s="2" t="n">
-        <v>3985.73</v>
+        <v>3966.14</v>
       </c>
     </row>
     <row r="1040">
@@ -63907,7 +63907,7 @@
         </is>
       </c>
       <c r="M1040" s="2" t="n">
-        <v>2581.03</v>
+        <v>2568.34</v>
       </c>
     </row>
     <row r="1041">
@@ -63968,7 +63968,7 @@
         </is>
       </c>
       <c r="M1041" s="2" t="n">
-        <v>2396.13</v>
+        <v>2384.35</v>
       </c>
     </row>
     <row r="1042">
@@ -64029,7 +64029,7 @@
         </is>
       </c>
       <c r="M1042" s="2" t="n">
-        <v>5228.63</v>
+        <v>5202.92</v>
       </c>
     </row>
     <row r="1043">
@@ -64090,7 +64090,7 @@
         </is>
       </c>
       <c r="M1043" s="2" t="n">
-        <v>8732.540000000001</v>
+        <v>8689.610000000001</v>
       </c>
     </row>
     <row r="1044">
@@ -64151,7 +64151,7 @@
         </is>
       </c>
       <c r="M1044" s="2" t="n">
-        <v>2047.13</v>
+        <v>2037.07</v>
       </c>
     </row>
     <row r="1045">
@@ -64212,7 +64212,7 @@
         </is>
       </c>
       <c r="M1045" s="2" t="n">
-        <v>8521.92</v>
+        <v>8480.02</v>
       </c>
     </row>
     <row r="1046">
@@ -64273,7 +64273,7 @@
         </is>
       </c>
       <c r="M1046" s="2" t="n">
-        <v>811.79</v>
+        <v>807.8</v>
       </c>
     </row>
     <row r="1047">
@@ -64334,7 +64334,7 @@
         </is>
       </c>
       <c r="M1047" s="2" t="n">
-        <v>2011.18</v>
+        <v>2001.29</v>
       </c>
     </row>
     <row r="1048">
@@ -64395,7 +64395,7 @@
         </is>
       </c>
       <c r="M1048" s="2" t="n">
-        <v>912.3200000000001</v>
+        <v>907.83</v>
       </c>
     </row>
     <row r="1049">
@@ -64456,7 +64456,7 @@
         </is>
       </c>
       <c r="M1049" s="2" t="n">
-        <v>20832.6</v>
+        <v>20730.17</v>
       </c>
     </row>
     <row r="1050">
@@ -64517,7 +64517,7 @@
         </is>
       </c>
       <c r="M1050" s="2" t="n">
-        <v>2299.89</v>
+        <v>2288.58</v>
       </c>
     </row>
     <row r="1051">
@@ -64578,7 +64578,7 @@
         </is>
       </c>
       <c r="M1051" s="2" t="n">
-        <v>6249.94</v>
+        <v>6291.77</v>
       </c>
     </row>
     <row r="1052">
@@ -64639,7 +64639,7 @@
         </is>
       </c>
       <c r="M1052" s="2" t="n">
-        <v>1481</v>
+        <v>1490.91</v>
       </c>
     </row>
     <row r="1053">
@@ -64700,7 +64700,7 @@
         </is>
       </c>
       <c r="M1053" s="2" t="n">
-        <v>9662.25</v>
+        <v>9726.92</v>
       </c>
     </row>
     <row r="1054">
@@ -64761,7 +64761,7 @@
         </is>
       </c>
       <c r="M1054" s="2" t="n">
-        <v>32359.25</v>
+        <v>32575.85</v>
       </c>
     </row>
     <row r="1055">
@@ -64822,7 +64822,7 @@
         </is>
       </c>
       <c r="M1055" s="2" t="n">
-        <v>10272.43</v>
+        <v>10341.19</v>
       </c>
     </row>
     <row r="1056">
@@ -64883,7 +64883,7 @@
         </is>
       </c>
       <c r="M1056" s="2" t="n">
-        <v>1689.79</v>
+        <v>1701.1</v>
       </c>
     </row>
     <row r="1057">
@@ -64944,7 +64944,7 @@
         </is>
       </c>
       <c r="M1057" s="2" t="n">
-        <v>992.9400000000001</v>
+        <v>999.59</v>
       </c>
     </row>
     <row r="1058">
@@ -65005,7 +65005,7 @@
         </is>
       </c>
       <c r="M1058" s="2" t="n">
-        <v>3297.85</v>
+        <v>3319.92</v>
       </c>
     </row>
     <row r="1059">
@@ -65066,7 +65066,7 @@
         </is>
       </c>
       <c r="M1059" s="2" t="n">
-        <v>2107.17</v>
+        <v>2121.28</v>
       </c>
     </row>
     <row r="1060">
@@ -65127,7 +65127,7 @@
         </is>
       </c>
       <c r="M1060" s="2" t="n">
-        <v>1609.51</v>
+        <v>1620.29</v>
       </c>
     </row>
     <row r="1061">
@@ -65188,7 +65188,7 @@
         </is>
       </c>
       <c r="M1061" s="2" t="n">
-        <v>1722.46</v>
+        <v>1733.99</v>
       </c>
     </row>
     <row r="1062">
@@ -65249,7 +65249,7 @@
         </is>
       </c>
       <c r="M1062" s="2" t="n">
-        <v>2336.41</v>
+        <v>2352.05</v>
       </c>
     </row>
     <row r="1063">
@@ -65310,7 +65310,7 @@
         </is>
       </c>
       <c r="M1063" s="2" t="n">
-        <v>3376.32</v>
+        <v>3398.92</v>
       </c>
     </row>
     <row r="1064">
@@ -65371,7 +65371,7 @@
         </is>
       </c>
       <c r="M1064" s="2" t="n">
-        <v>2289.77</v>
+        <v>2305.1</v>
       </c>
     </row>
     <row r="1065">
@@ -65432,7 +65432,7 @@
         </is>
       </c>
       <c r="M1065" s="2" t="n">
-        <v>2608.56</v>
+        <v>2626.02</v>
       </c>
     </row>
     <row r="1066">
@@ -65493,7 +65493,7 @@
         </is>
       </c>
       <c r="M1066" s="2" t="n">
-        <v>2588.87</v>
+        <v>2606.2</v>
       </c>
     </row>
     <row r="1067">
@@ -65554,7 +65554,7 @@
         </is>
       </c>
       <c r="M1067" s="2" t="n">
-        <v>5028.42</v>
+        <v>5062.08</v>
       </c>
     </row>
     <row r="1068">
@@ -65615,7 +65615,7 @@
         </is>
       </c>
       <c r="M1068" s="2" t="n">
-        <v>2651.96</v>
+        <v>2669.71</v>
       </c>
     </row>
     <row r="1069">
@@ -65676,7 +65676,7 @@
         </is>
       </c>
       <c r="M1069" s="2" t="n">
-        <v>792.78</v>
+        <v>798.09</v>
       </c>
     </row>
     <row r="1070">
@@ -65737,7 +65737,7 @@
         </is>
       </c>
       <c r="M1070" s="2" t="n">
-        <v>24031.21</v>
+        <v>24192.07</v>
       </c>
     </row>
     <row r="1071">
@@ -65798,7 +65798,7 @@
         </is>
       </c>
       <c r="M1071" s="2" t="n">
-        <v>2335.98</v>
+        <v>2351.61</v>
       </c>
     </row>
     <row r="1072">
@@ -65859,7 +65859,7 @@
         </is>
       </c>
       <c r="M1072" s="2" t="n">
-        <v>2703</v>
+        <v>2721.1</v>
       </c>
     </row>
     <row r="1073">
@@ -65920,7 +65920,7 @@
         </is>
       </c>
       <c r="M1073" s="2" t="n">
-        <v>87591.19</v>
+        <v>88177.48</v>
       </c>
     </row>
     <row r="1074">
@@ -65981,7 +65981,7 @@
         </is>
       </c>
       <c r="M1074" s="2" t="n">
-        <v>789.02</v>
+        <v>794.3</v>
       </c>
     </row>
     <row r="1075">
@@ -66042,7 +66042,7 @@
         </is>
       </c>
       <c r="M1075" s="2" t="n">
-        <v>860.98</v>
+        <v>866.74</v>
       </c>
     </row>
     <row r="1076">
@@ -66103,7 +66103,7 @@
         </is>
       </c>
       <c r="M1076" s="2" t="n">
-        <v>2845.49</v>
+        <v>2864.54</v>
       </c>
     </row>
     <row r="1077">
@@ -66164,7 +66164,7 @@
         </is>
       </c>
       <c r="M1077" s="2" t="n">
-        <v>6654.46</v>
+        <v>6699</v>
       </c>
     </row>
     <row r="1078">
@@ -66225,7 +66225,7 @@
         </is>
       </c>
       <c r="M1078" s="2" t="n">
-        <v>3704.07</v>
+        <v>3728.87</v>
       </c>
     </row>
     <row r="1079">
@@ -66286,7 +66286,7 @@
         </is>
       </c>
       <c r="M1079" s="2" t="n">
-        <v>2760.62</v>
+        <v>2779.1</v>
       </c>
     </row>
     <row r="1080">
@@ -66347,7 +66347,7 @@
         </is>
       </c>
       <c r="M1080" s="2" t="n">
-        <v>1693.12</v>
+        <v>1704.45</v>
       </c>
     </row>
     <row r="1081">
@@ -66408,7 +66408,7 @@
         </is>
       </c>
       <c r="M1081" s="2" t="n">
-        <v>1827.69</v>
+        <v>1839.92</v>
       </c>
     </row>
     <row r="1082">
@@ -66469,7 +66469,7 @@
         </is>
       </c>
       <c r="M1082" s="2" t="n">
-        <v>1453.13</v>
+        <v>1462.85</v>
       </c>
     </row>
     <row r="1083">
@@ -66530,7 +66530,7 @@
         </is>
       </c>
       <c r="M1083" s="2" t="n">
-        <v>12840.49</v>
+        <v>12926.44</v>
       </c>
     </row>
     <row r="1084">
@@ -66591,7 +66591,7 @@
         </is>
       </c>
       <c r="M1084" s="2" t="n">
-        <v>13303.5</v>
+        <v>13392.55</v>
       </c>
     </row>
     <row r="1085">
@@ -66652,7 +66652,7 @@
         </is>
       </c>
       <c r="M1085" s="2" t="n">
-        <v>3090.58</v>
+        <v>3111.27</v>
       </c>
     </row>
     <row r="1086">
@@ -66713,7 +66713,7 @@
         </is>
       </c>
       <c r="M1086" s="2" t="n">
-        <v>3415.48</v>
+        <v>3438.34</v>
       </c>
     </row>
     <row r="1087">
@@ -66774,7 +66774,7 @@
         </is>
       </c>
       <c r="M1087" s="2" t="n">
-        <v>5019.71</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="1088">
@@ -66835,7 +66835,7 @@
         </is>
       </c>
       <c r="M1088" s="2" t="n">
-        <v>2995.14</v>
+        <v>3015.19</v>
       </c>
     </row>
     <row r="1089">
@@ -66896,7 +66896,7 @@
         </is>
       </c>
       <c r="M1089" s="2" t="n">
-        <v>1353.38</v>
+        <v>1362.44</v>
       </c>
     </row>
     <row r="1090">
@@ -66957,7 +66957,7 @@
         </is>
       </c>
       <c r="M1090" s="2" t="n">
-        <v>2713.91</v>
+        <v>2732.07</v>
       </c>
     </row>
     <row r="1091">
@@ -67018,7 +67018,7 @@
         </is>
       </c>
       <c r="M1091" s="2" t="n">
-        <v>8501.23</v>
+        <v>8558.139999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30809,7 +30809,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -31053,7 +31053,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31068,7 +31068,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38331,7 +38331,7 @@
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -38625,7 +38625,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38991,7 +38991,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -40211,7 +40211,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40272,7 +40272,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40577,7 +40577,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40699,7 +40699,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40760,7 +40760,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -41065,7 +41065,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41736,7 +41736,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -42773,7 +42773,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -43200,7 +43200,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43444,7 +43444,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43749,7 +43749,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -45152,7 +45152,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45579,7 +45579,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45701,7 +45701,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45945,7 +45945,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46128,7 +46128,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46311,7 +46311,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46616,7 +46616,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46936,7 +46936,7 @@
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L762" t="inlineStr">
@@ -46986,7 +46986,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -48084,7 +48084,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48206,7 +48206,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -49243,7 +49243,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49304,7 +49304,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -49792,7 +49792,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50219,7 +50219,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -50341,7 +50341,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -50829,7 +50829,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -52415,7 +52415,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -52903,7 +52903,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -53269,7 +53269,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53391,7 +53391,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -53452,7 +53452,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -53513,7 +53513,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -54489,7 +54489,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54611,7 +54611,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -55343,7 +55343,7 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -55465,7 +55465,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -55587,7 +55587,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -56075,7 +56075,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -56502,7 +56502,7 @@
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
@@ -56624,7 +56624,7 @@
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -56868,7 +56868,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -57051,7 +57051,7 @@
       </c>
       <c r="H928" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I928" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="H930" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I930" t="inlineStr">
@@ -57539,7 +57539,7 @@
       </c>
       <c r="H936" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
@@ -57905,7 +57905,7 @@
       </c>
       <c r="H942" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I942" t="inlineStr">
@@ -58759,7 +58759,7 @@
       </c>
       <c r="H956" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I956" t="inlineStr">
@@ -59064,7 +59064,7 @@
       </c>
       <c r="H961" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I961" t="inlineStr">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="H972" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I972" t="inlineStr">
@@ -59918,7 +59918,7 @@
       </c>
       <c r="H975" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
@@ -60284,7 +60284,7 @@
       </c>
       <c r="H981" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I981" t="inlineStr">
@@ -60467,7 +60467,7 @@
       </c>
       <c r="H984" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I984" t="inlineStr">
@@ -60589,7 +60589,7 @@
       </c>
       <c r="H986" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I986" t="inlineStr">
@@ -60772,7 +60772,7 @@
       </c>
       <c r="H989" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I989" t="inlineStr">
@@ -60909,7 +60909,7 @@
       </c>
       <c r="K991" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L991" t="inlineStr">
@@ -61142,7 +61142,7 @@
       </c>
       <c r="H995" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I995" t="inlineStr">
@@ -61325,7 +61325,7 @@
       </c>
       <c r="H998" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I998" t="inlineStr">
@@ -61874,7 +61874,7 @@
       </c>
       <c r="H1007" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1007" t="inlineStr">
@@ -62057,7 +62057,7 @@
       </c>
       <c r="H1010" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1010" t="inlineStr">
@@ -62179,7 +62179,7 @@
       </c>
       <c r="H1012" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1012" t="inlineStr">
@@ -62362,7 +62362,7 @@
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
@@ -63155,7 +63155,7 @@
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
@@ -63521,7 +63521,7 @@
       </c>
       <c r="H1034" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1034" t="inlineStr">
@@ -63704,7 +63704,7 @@
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
@@ -65107,7 +65107,7 @@
       </c>
       <c r="H1060" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1060" t="inlineStr">
@@ -65900,7 +65900,7 @@
       </c>
       <c r="H1073" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I1073" t="inlineStr">
@@ -66327,7 +66327,7 @@
       </c>
       <c r="H1080" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I1080" t="inlineStr">
@@ -66815,7 +66815,7 @@
       </c>
       <c r="H1088" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1088" t="inlineStr">
@@ -66876,7 +66876,7 @@
       </c>
       <c r="H1089" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I1089" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2026.xlsx
@@ -822,7 +822,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -883,7 +887,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1651,7 +1659,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1773,7 +1785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2728,7 +2744,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3049,7 +3069,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3675,7 +3699,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5475,7 +5503,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6170,7 +6202,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6231,7 +6267,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6588,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6609,7 +6653,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7121,7 +7169,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8015,7 +8067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8202,7 +8258,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9360,7 +9420,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11591,7 +11655,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12359,7 +12427,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14480,7 +14552,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15443,7 +15519,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15569,7 +15649,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15886,7 +15970,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17166,7 +17254,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19486,7 +19578,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20189,7 +20285,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21603,7 +21703,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21985,7 +22089,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22497,7 +22605,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22948,7 +23060,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23399,7 +23515,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23907,7 +24027,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24094,7 +24218,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24797,7 +24925,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25947,7 +26079,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26073,7 +26209,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26780,7 +26920,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26841,7 +26985,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27227,7 +27375,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28133,7 +28285,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28259,7 +28415,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28897,7 +29057,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30303,7 +30467,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31136,7 +31304,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31262,7 +31434,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31384,7 +31560,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31953,7 +32133,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32916,7 +33100,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34074,7 +34262,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34135,7 +34327,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34452,7 +34648,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34773,7 +34973,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35090,7 +35294,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35277,7 +35485,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36045,7 +36257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37841,7 +38057,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38739,7 +38959,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39113,7 +39337,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39300,7 +39528,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39487,7 +39719,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40068,7 +40304,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40905,7 +41145,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42429,7 +42673,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43392,7 +43640,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45903,7 +46155,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46220,7 +46476,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46281,7 +46541,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47053,7 +47317,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48325,7 +48593,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48768,7 +49040,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48829,7 +49105,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50113,7 +50393,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L777" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50560,7 +50844,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51710,7 +51998,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53173,7 +53465,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53815,7 +54111,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55404,7 +55704,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58017,7 +58321,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58273,7 +58581,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58984,7 +59296,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60179,7 +60495,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60366,7 +60686,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60882,7 +61206,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -62215,7 +62543,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -63036,7 +63368,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64125,7 +64461,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr"/>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L997" t="inlineStr">
         <is>
           <t>USD</t>
@@ -64629,7 +64969,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1005" t="inlineStr"/>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1005" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66039,7 +66383,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1027" t="inlineStr"/>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1027" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66421,7 +66769,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1033" t="inlineStr"/>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1033" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66612,7 +66964,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1036" t="inlineStr"/>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1036" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67892,7 +68248,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1056" t="inlineStr"/>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1056" t="inlineStr">
         <is>
           <t>USD</t>
@@ -68526,7 +68886,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1066" t="inlineStr"/>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1066" t="inlineStr">
         <is>
           <t>USD</t>
@@ -70302,7 +70666,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K1094" t="inlineStr"/>
+      <c r="K1094" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1094" t="inlineStr">
         <is>
           <t>USD</t>
